--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>12 sprints, each a distinct TEST DIMENSION. Each backlog row is a concrete scenario with an expected result, grounded in the real code (mapped 2026-08-29). Automatable rows become pytest; scenario rows become scripted E2E / manual runbooks. Priority: isolation, RBAC, formula correctness, regression-health = P0.</t>
+          <t>13 sprints, each a distinct TEST DIMENSION. TESTING = FRONTEND AS WELL AS BACKEND: every functional (S2) + E2E (S12) scenario also gets a browser-driven variant, and S13 tests the whole UI surface (buttons/forms/nav/states/role-gated UI/responsive) in the browser preview. Onboarding (S4) is treated as the founder's first-impression journey -- per-niche workflow-generation quality, interview prompt+question quality, back-navigate-and-re-answer, and the 'feeling' UX bar are first-class rows. Each backlog row is a concrete scenario with an expected result, grounded in the real code (mapped 2026-08-29). Automatable rows become pytest; UI/journey rows become browser-driven (Browser-pane) + scripted E2E. Priority: isolation, RBAC, formula correctness, onboarding-journey, FE buttons/nav/role-gating, regression-health = P0.</t>
         </is>
       </c>
     </row>
@@ -997,6 +997,37 @@
         </is>
       </c>
       <c r="B62" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Sprint 13 -- Frontend / UX / browser-driven</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Testing = frontend AS WELL AS backend. Drive the REAL UI in the browser preview: every button/form/nav/state, role-gated UI, responsive/mobile, empty/loading/error states, console+network health, the karma design-system, and the founder 'feeling'. Every functional + E2E scenario also gets a browser-driven variant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
@@ -1013,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1042,7 +1073,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Epic 10 -- Testing PLANNED. 12 sprints, 134 scenario tasks scoped from a full code map (roles, formulas, modules, tenancy, concurrency). Builds on Epic 1's Testing Plan (phases A-J) + Go-Live Checklist. Execution picked up sprint by sprint; isolation / RBAC / formula / regression-health are the P0 lanes.</t>
+          <t>Epic 10 -- Testing PLANNED. 12 sprints, 154 scenario tasks scoped from a full code map (roles, formulas, modules, tenancy, concurrency). Builds on Epic 1's Testing Plan (phases A-J) + Go-Live Checklist. Execution picked up sprint by sprint; isolation / RBAC / formula / regression-health are the P0 lanes.</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -1476,6 +1507,39 @@
       <c r="G17" s="12" t="inlineStr">
         <is>
           <t>Golden-path journeys per persona (owner/finance/sales/ops), WhatsApp-&gt;action, voice-&gt;decision-&gt;done; map the Testing-Plan phase A-J exit criteria; go-live testing sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Frontend / UX / browser-driven</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Testing = frontend AS WELL AS backend. Drive the REAL UI in the browser preview: every button/form/nav/state, role-gated UI, responsive/mobile, empty/loading/error states, console+network health, the karma design-system, and the founder 'feeling'. Every functional + E2E scenario also gets a browser-driven variant.</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L135"/>
+  <dimension ref="A1:L155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4148,40 +4212,40 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>T10-05.1</t>
+          <t>T10-04.11</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>seed / onboarding</t>
+          <t>routers/onboarding.py + signup</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Multi-niche</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Textile manufacturing (Sharma baseline)</t>
+          <t>Per-niche workflow/OS GENERATION QUALITY</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>The seeded demo: production/distribution/purchase_payment pipelines, 4 roles. Full flow: bill-&gt;classify-&gt;match, task-&gt;done, decision-&gt;approve. The regression baseline niche.</t>
-        </is>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>THE CORE ONBOARDING TEST. Onboard a restaurant, a clinic, a logistics/cold-chain, a textile, a retail business -&gt; for EACH, assert the AI-generated operating model (pipelines + stages + roles + recurring tasks) actually FITS that business and is NOT a generic/textile template. Rubric-scored per niche; the generated workflow is the founder's first proof the product 'gets' them.</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -4204,35 +4268,35 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>T10-05.2</t>
+          <t>T10-04.12</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>onboarding</t>
+          <t>routers/signup.py (interview prompt)</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Multi-niche</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Logistics / cold-chain (Tracole)</t>
+          <t>Interview QUESTION quality + count</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>Industry 'Logistics &amp; Transport'. Custom role (consignee_liaison). Assert AI generates a distinct pipeline (dispatch/delivery), no textile assumptions leak.</t>
-        </is>
-      </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Validate the Dex interview asks GOOD, relevant, non-redundant questions and stops at the right depth (2-6 adaptive). Does it end too early (thin blueprint) or drag? Per founder-persona, score question relevance + whether the resulting OS is richer for a good question set. Are 2-3 questions actually enough?</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -4260,35 +4324,35 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>T10-05.3</t>
+          <t>T10-04.13</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>onboarding</t>
+          <t>prompts/ registry + signup</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Multi-niche</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Electronics manufacturing (Volt Circuit)</t>
+          <t>Onboarding PROMPT tunability + no-regression</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>Industry Manufacturing/Technology. BOM/inventory-heavy. Assert inventory unit_cost math + asset tracking fit a components business.</t>
-        </is>
-      </c>
-      <c r="G50" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>We WILL tune the interview/blueprint prompts. Build a golden-set of founder personas (per niche) so a prompt change re-runs them and output quality is diffed -- prompt improves without regressing other niches. Ties to Epic 3 prompt registry.</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -4316,35 +4380,35 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>T10-05.4</t>
+          <t>T10-04.14</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>onboarding</t>
+          <t>onboarding/VoiceInterview.js + /interview/back</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Multi-niche</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Restaurant / F&amp;B</t>
+          <t>Back-navigate + RE-ANSWER a question</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>Daily cash sales, perishable inventory, few formal invoices. Assert operating score + finance handle high-volume small-ticket + no-invoice days.</t>
-        </is>
-      </c>
-      <c r="G51" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>THE founder-described scenario: answer Q1 (voice), realize a mistake, go BACK to that exact question, re-speak/re-type a new answer -&gt; assert the transcript is corrected AND the downstream blueprint reflects the NEW answer, not the stale one. No duplicate/orphan answer state.</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
@@ -4372,35 +4436,35 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>T10-05.5</t>
+          <t>T10-04.15</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>onboarding</t>
+          <t>onboarding/BuildReveal.js + /interview/refine</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Multi-niche</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Healthcare / clinic</t>
+          <t>Refine loop (voice/text) re-blueprints</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>Appointment-driven, no 'sales pipeline', privacy-sensitive. Assert AI generates a non-sales operating model + Brain doc visibility holds for patient-ish data.</t>
-        </is>
-      </c>
-      <c r="G52" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>After preview, founder refines by voice or text ('add a returns workflow') -&gt; re-runs blueprint -&gt; assert the refinement is incorporated and the reveal updates. Refine twice, assert cumulative.</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
@@ -4428,40 +4492,40 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>T10-05.6</t>
+          <t>T10-04.16</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>onboarding</t>
+          <t>BROWSER preview (FE+BE)</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Multi-niche</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Retail / e-commerce</t>
+          <t>Browser-driven full onboarding journey</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>High transaction volume, many small payments. Stress payment-matching + outstanding aggregation at volume within one tenant.</t>
-        </is>
-      </c>
-      <c r="G53" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Drive the ACTUAL onboarding UI in the browser preview end to end: every step's buttons, email-check, password rules, language pick, voice record/stop, Skip, Back, build-&gt;preview-&gt;register-&gt;reveal. Assert BOTH the UI behaves (no dead buttons, right transitions) AND backend state matches at each step. FE + BE together, not API-only.</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -4484,35 +4548,35 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>T10-05.7</t>
+          <t>T10-04.17</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>onboarding</t>
+          <t>BROWSER preview</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Multi-niche</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Pharma distribution</t>
+          <t>Founder first-impression / 'feeling' UX bar</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>Batch/expiry, GST-heavy invoices. NOTE: no GST math exists -&gt; assert gross amounts handled as-is, tax-inclusive vs base treated as unrelated numbers.</t>
-        </is>
-      </c>
-      <c r="G54" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Onboarding must FEEL premium + reassuring -- it's the founder's first moment with the product. Heuristic review against a rubric: smooth transitions + loading states, an earned reveal moment, warm on-brand copy, zero dead-ends, no jarring error, momentum never lost. The emotional-quality gate, checked in-browser.</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
@@ -4540,40 +4604,40 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>T10-05.8</t>
+          <t>T10-04.18</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>onboarding</t>
+          <t>onboarding voice UI (FE+BE)</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Multi-niche</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Professional services / consulting</t>
+          <t>Voice-capture UX in onboarding</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>Time/retainer-based, no inventory. Assert operating model has no inventory pipeline + finance handles recurring retainers.</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Mic permission prompt, recording indicator, transcription latency, Tanglish/accent handling, retry on failed transcription, and graceful fallback to typing when voice fails. The voice path is the wow-moment -- it must never strand the founder.</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -4596,12 +4660,12 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>T10-05.9</t>
+          <t>T10-05.1</t>
         </is>
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>onboarding</t>
+          <t>seed / onboarding</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
@@ -4614,22 +4678,22 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Textile manufacturing (Sharma baseline)</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>Project milestones, large staged payments. Assert partial-payment matching + workflow stages fit milestone billing.</t>
-        </is>
-      </c>
-      <c r="G56" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>The seeded demo: production/distribution/purchase_payment pipelines, 4 roles. Full flow: bill-&gt;classify-&gt;match, task-&gt;done, decision-&gt;approve. The regression baseline niche.</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -4652,7 +4716,7 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>T10-05.10</t>
+          <t>T10-05.2</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
@@ -4670,22 +4734,22 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Agriculture (seasonal)</t>
+          <t>Logistics / cold-chain (Tracole)</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>Seasonal/commodity. Assert follow-up/escalation timing + operating score don't misfire on seasonal gaps.</t>
-        </is>
-      </c>
-      <c r="G57" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Industry 'Logistics &amp; Transport'. Custom role (consignee_liaison). Assert AI generates a distinct pipeline (dispatch/delivery), no textile assumptions leak.</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -4708,7 +4772,7 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>T10-05.11</t>
+          <t>T10-05.3</t>
         </is>
       </c>
       <c r="B58" s="12" t="inlineStr">
@@ -4726,12 +4790,12 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Custom 'Other' free-text industry</t>
+          <t>Electronics manufacturing (Volt Circuit)</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>Free-text industry not in the 26 -&gt; AI must still generate a coherent operating model + roles. Assert no crash + sensible defaults.</t>
+          <t>Industry Manufacturing/Technology. BOM/inventory-heavy. Assert inventory unit_cost math + asset tracking fit a components business.</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr">
@@ -4741,7 +4805,7 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -4764,7 +4828,7 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>T10-05.12</t>
+          <t>T10-05.4</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
@@ -4782,12 +4846,12 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Per-niche generation assertion</t>
+          <t>Restaurant / F&amp;B</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>Sweep all niches: assert each yields DISTINCT workflows + roles (not a textile template copy). The multi-niche generation-quality gate.</t>
+          <t>Daily cash sales, perishable inventory, few formal invoices. Assert operating score + finance handle high-volume small-ticket + no-invoice days.</t>
         </is>
       </c>
       <c r="G59" s="15" t="inlineStr">
@@ -4820,40 +4884,40 @@
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>T10-06.1</t>
+          <t>T10-05.5</t>
         </is>
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Multi-niche</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Solo owner (1 user)</t>
+          <t>Healthcare / clinic</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>Everything works with a single owner: operating score returns company + self, no divide-by-zero on empty team, dashboards render.</t>
-        </is>
-      </c>
-      <c r="G60" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Appointment-driven, no 'sales pipeline', privacy-sensitive. Assert AI generates a non-sales operating model + Brain doc visibility holds for patient-ish data.</t>
+        </is>
+      </c>
+      <c r="G60" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -4876,35 +4940,35 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>T10-06.2</t>
+          <t>T10-05.6</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>routers/team.py + plans.py</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Multi-niche</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>10-member team (starter cap)</t>
+          <t>Retail / e-commerce</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>Invite up to 10 on starter; 11th -&gt; 402 seat_limit_reached. Assert cap counts active memberships incl. owner.</t>
-        </is>
-      </c>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>High transaction volume, many small payments. Stress payment-matching + outstanding aggregation at volume within one tenant.</t>
+        </is>
+      </c>
+      <c r="G61" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
@@ -4932,30 +4996,30 @@
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>T10-06.3</t>
+          <t>T10-05.7</t>
         </is>
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>routers/team.py</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Multi-niche</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>20-member team (business plan)</t>
+          <t>Pharma distribution</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>Set plan=business (or seat_limit_override), provision 20. Per-role dashboards each scoped correctly; operating-score per-employee list holds.</t>
+          <t>Batch/expiry, GST-heavy invoices. NOTE: no GST math exists -&gt; assert gross amounts handled as-is, tax-inclusive vs base treated as unrelated numbers.</t>
         </is>
       </c>
       <c r="G62" s="15" t="inlineStr">
@@ -4988,40 +5052,40 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>T10-06.4</t>
+          <t>T10-05.8</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>routers/team.py</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Multi-niche</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>30-member team (business)</t>
+          <t>Professional services / consulting</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>Provision 30; assert operating-score _score_employees at scale, unassigned-role-task double-count behavior visible, list caps (2000 tasks) respected.</t>
-        </is>
-      </c>
-      <c r="G63" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Time/retainer-based, no inventory. Assert operating model has no inventory pipeline + finance handles recurring retainers.</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -5044,40 +5108,40 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>T10-06.5</t>
+          <t>T10-05.9</t>
         </is>
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>multiple</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Multi-niche</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>30 members working in parallel</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>30 concurrent sessions doing task creates/updates/finance posts. Assert no lost writes, per-tenant throttle behavior, dashboards consistent.</t>
-        </is>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Project milestones, large staged payments. Assert partial-payment matching + workflow stages fit milestone billing.</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -5100,40 +5164,40 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>T10-06.6</t>
+          <t>T10-05.10</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>services/plans.py</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Multi-niche</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Seat-limit race (TOCTOU)</t>
+          <t>Agriculture (seasonal)</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>N parallel invites at cap 10/10 -&gt; enforce_seat_limit is count-then-insert with no atomic reservation -&gt; EXPOSE over-provision. High-value concurrency test.</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>Seasonal/commodity. Assert follow-up/escalation timing + operating score don't misfire on seasonal gaps.</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -5156,40 +5220,40 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>T10-06.7</t>
+          <t>T10-05.11</t>
         </is>
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>multiple</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Multi-niche</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Per-role dashboard isolation at scale</t>
+          <t>Custom 'Other' free-text industry</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>Each of 30 members sees ONLY their scoped data (own tasks/team lane), owner sees all. No cross-member leakage in lists.</t>
-        </is>
-      </c>
-      <c r="G66" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Free-text industry not in the 26 -&gt; AI must still generate a coherent operating model + roles. Assert no crash + sensible defaults.</t>
+        </is>
+      </c>
+      <c r="G66" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
@@ -5212,35 +5276,35 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>T10-06.8</t>
+          <t>T10-05.12</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>services/quotas.py</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Multi-niche</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Quota walls under load</t>
+          <t>Per-niche generation assertion</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>30 members hammering AI -&gt; llm_tokens_total/stt_minutes hit cap -&gt; 402 on non-enterprise. Assert enforcement + fail-open gap under burst.</t>
-        </is>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Sweep all niches: assert each yields DISTINCT workflows + roles (not a textile template copy). The multi-niche generation-quality gate.</t>
+        </is>
+      </c>
+      <c r="G67" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
@@ -5268,12 +5332,12 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>T10-06.9</t>
+          <t>T10-06.1</t>
         </is>
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>routers/auth_otp.py</t>
+          <t>all</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
@@ -5286,22 +5350,22 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Invite flow at scale</t>
+          <t>Solo owner (1 user)</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>30 OTP invites: 7-day expiry, single-use consumption, 30s resend cooldown, no cross-tenant leak in ambiguous resolution.</t>
-        </is>
-      </c>
-      <c r="G68" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Everything works with a single owner: operating score returns company + self, no divide-by-zero on empty team, dashboards render.</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -5324,12 +5388,12 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>T10-06.10</t>
+          <t>T10-06.2</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>routers/team.py</t>
+          <t>routers/team.py + plans.py</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
@@ -5342,17 +5406,17 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Deprovision at scale</t>
+          <t>10-member team (starter cap)</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>Remove members: sessions revoked, membership removed, tasks+contacts reassigned, no orphans. Last-owner guard holds.</t>
-        </is>
-      </c>
-      <c r="G69" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Invite up to 10 on starter; 11th -&gt; 402 seat_limit_reached. Assert cap counts active memberships incl. owner.</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
@@ -5380,40 +5444,40 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>T10-07.1</t>
+          <t>T10-06.3</t>
         </is>
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>services/operating_score.py</t>
+          <t>routers/team.py</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Formula/Edge</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>overall None&lt;-&gt;70 discontinuity</t>
+          <t>20-member team (business plan)</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>At exactly actionable 2-&gt;3 and inv_count 0-&gt;1 the company overall flips None-&gt;a number while sub-scores sat at 70. Assert the boundary + document expected UX.</t>
-        </is>
-      </c>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>Set plan=business (or seat_limit_override), provision 20. Per-role dashboards each scoped correctly; operating-score per-employee list holds.</t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
@@ -5436,35 +5500,35 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>T10-07.2</t>
+          <t>T10-06.4</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>operating_score vs finance_signals</t>
+          <t>routers/team.py</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Formula/Edge</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Empty due_date inconsistency</t>
+          <t>30-member team (business)</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>Blank due_date: NEVER overdue in operating_score (''&lt;now string) but IS overdue in finance_signals (''[:10]&lt;=cutoff). Same field, two behaviors. Assert + reconcile.</t>
-        </is>
-      </c>
-      <c r="G71" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>Provision 30; assert operating-score _score_employees at scale, unassigned-role-task double-count behavior visible, list caps (2000 tasks) respected.</t>
+        </is>
+      </c>
+      <c r="G71" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -5492,30 +5556,30 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>T10-07.3</t>
+          <t>T10-06.5</t>
         </is>
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>services/operating_score.py</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Formula/Edge</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Employee vs company default asymmetry</t>
+          <t>30 members working in parallel</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>Company completion defaults 0.7; employee defaults 0 and score None when zero tasks. Assert the asymmetry is intentional/tested.</t>
+          <t>30 concurrent sessions doing task creates/updates/finance posts. Assert no lost writes, per-tenant throttle behavior, dashboards consistent.</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
@@ -5525,7 +5589,7 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -5548,40 +5612,40 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>T10-07.4</t>
+          <t>T10-06.6</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>services/operating_score.py</t>
+          <t>services/plans.py</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Formula/Edge</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>total_paid sums ALL payments</t>
+          <t>Seat-limit race (TOCTOU)</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>finance sub-score total_paid sums payments regardless of direction -&gt; out-payments inflate 'collected'. Feed out-payments, assert the inflation (bug candidate).</t>
-        </is>
-      </c>
-      <c r="G73" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>N parallel invites at cap 10/10 -&gt; enforce_seat_limit is count-then-insert with no atomic reservation -&gt; EXPOSE over-provision. High-value concurrency test.</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
@@ -5604,30 +5668,30 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>T10-07.5</t>
+          <t>T10-06.7</t>
         </is>
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t>services/operating_score.py</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Formula/Edge</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Unassigned task double-count</t>
+          <t>Per-role dashboard isolation at scale</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>A role-only task with N teammates is counted for EVERY member in _score_employees, inflating N scores. Assert with a 5-member role.</t>
+          <t>Each of 30 members sees ONLY their scoped data (own tasks/team lane), owner sees all. No cross-member leakage in lists.</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
@@ -5637,7 +5701,7 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -5660,30 +5724,30 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>T10-07.6</t>
+          <t>T10-06.8</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>routers/ledger.py</t>
+          <t>services/quotas.py</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Formula/Edge</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Indian amount parsing matrix</t>
+          <t>Quota walls under load</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>'Rs2.5 lakh'-&gt;250000, '1,20,000'-&gt;120000, '5 cr'-&gt;5e7, '999 crore'-&gt;9.99e9 (no overflow guard), negatives accepted. Table-driven.</t>
+          <t>30 members hammering AI -&gt; llm_tokens_total/stt_minutes hit cap -&gt; 402 on non-enterprise. Assert enforcement + fail-open gap under burst.</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
@@ -5693,7 +5757,7 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
@@ -5716,40 +5780,40 @@
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>T10-07.7</t>
+          <t>T10-06.9</t>
         </is>
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>services/ingestion.py</t>
+          <t>routers/auth_otp.py</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Formula/Edge</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Duplicate exact-float equality</t>
+          <t>Invite flow at scale</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>iamt==camt exact == : test 0.1+0.2, OCR decimals that don't round-trip -&gt; dup MISSED. Assert the fragility.</t>
-        </is>
-      </c>
-      <c r="G76" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>30 OTP invites: 7-day expiry, single-use consumption, 30s resend cooldown, no cross-tenant leak in ambiguous resolution.</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -5772,30 +5836,30 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>T10-07.8</t>
+          <t>T10-06.10</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>services/ingestion.py</t>
+          <t>routers/team.py</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Formula/Edge</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Dup date-window boundaries</t>
+          <t>Deprovision at scale</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>gap==7 (dup) vs gap==8 (not); unparseable date (gap None) -&gt; treated as dup; number-only pool capped 500 (dup beyond cap missed).</t>
+          <t>Remove members: sessions revoked, membership removed, tasks+contacts reassigned, no orphans. Last-owner guard holds.</t>
         </is>
       </c>
       <c r="G77" s="15" t="inlineStr">
@@ -5828,12 +5892,12 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>T10-07.9</t>
+          <t>T10-07.1</t>
         </is>
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>routers/ledger.py</t>
+          <t>services/operating_score.py</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
@@ -5846,22 +5910,22 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Payment-match ambiguity + smart-match</t>
+          <t>overall None&lt;-&gt;70 discontinuity</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>2+ invoices with same normalized number -&gt; None (human review, no auto-match). Smart-match needs same contact + exact balance + within 30 days.</t>
-        </is>
-      </c>
-      <c r="G78" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>At exactly actionable 2-&gt;3 and inv_count 0-&gt;1 the company overall flips None-&gt;a number while sub-scores sat at 70. Assert the boundary + document expected UX.</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -5884,12 +5948,12 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>T10-07.10</t>
+          <t>T10-07.2</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>routers/ledger.py</t>
+          <t>operating_score vs finance_signals</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
@@ -5902,22 +5966,22 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Settle epsilon 0.01</t>
+          <t>Empty due_date inconsistency</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>Invoice/payment settle at 0.01 tolerance: balances 0.005 (settled), 0.01 (settled), 0.011 (partial). Assert paid vs partial status transitions.</t>
-        </is>
-      </c>
-      <c r="G79" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Blank due_date: NEVER overdue in operating_score (''&lt;now string) but IS overdue in finance_signals (''[:10]&lt;=cutoff). Same field, two behaviors. Assert + reconcile.</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -5940,12 +6004,12 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>T10-07.11</t>
+          <t>T10-07.3</t>
         </is>
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>services/finance_signals.py</t>
+          <t>services/operating_score.py</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
@@ -5958,12 +6022,12 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Escalation ladder boundaries</t>
+          <t>Employee vs company default asymmetry</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>days=(now-due).days: &lt;1 L1 notify, &lt;2 L2, &lt;3 L3 manager, else L4 OWNER ALERT. Monotonic/idempotent (skip if target&lt;=stored). Test each boundary day.</t>
+          <t>Company completion defaults 0.7; employee defaults 0 and score None when zero tasks. Assert the asymmetry is intentional/tested.</t>
         </is>
       </c>
       <c r="G80" s="13" t="inlineStr">
@@ -5973,7 +6037,7 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
@@ -5996,12 +6060,12 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>T10-07.12</t>
+          <t>T10-07.4</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>services/captures.py</t>
+          <t>services/operating_score.py</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
@@ -6014,12 +6078,12 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Capture 50000 + text/voice never-auto</t>
+          <t>total_paid sums ALL payments</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>needs_owner at amount&gt;=50000; auto-file requires &lt;50000 strict AND is_document -&gt; 50000 never auto-files AND text/voice (is_document=False) can never auto-file even at low value.</t>
+          <t>finance sub-score total_paid sums payments regardless of direction -&gt; out-payments inflate 'collected'. Feed out-payments, assert the inflation (bug candidate).</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
@@ -6052,12 +6116,12 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>T10-07.13</t>
+          <t>T10-07.5</t>
         </is>
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>routers/ledger.py</t>
+          <t>services/operating_score.py</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
@@ -6070,12 +6134,12 @@
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>net_profit + mixed currency</t>
+          <t>Unassigned task double-count</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>net_profit=revenue BILLED - ALL expenses (not cash). Mixed-currency invoices summed with NO FX conversion. Assert both quirks explicitly.</t>
+          <t>A role-only task with N teammates is counted for EVERY member in _score_employees, inflating N scores. Assert with a 5-member role.</t>
         </is>
       </c>
       <c r="G82" s="13" t="inlineStr">
@@ -6108,12 +6172,12 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>T10-07.14</t>
+          <t>T10-07.6</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>services/operating_score.py</t>
+          <t>routers/ledger.py</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
@@ -6126,17 +6190,17 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Malformed amount reaches score</t>
+          <t>Indian amount parsing matrix</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>A non-numeric amount string on an invoice hits float(i.get('amount') or 0) with NO try/except in operating_score -&gt; raises. Assert + harden.</t>
-        </is>
-      </c>
-      <c r="G83" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>'Rs2.5 lakh'-&gt;250000, '1,20,000'-&gt;120000, '5 cr'-&gt;5e7, '999 crore'-&gt;9.99e9 (no overflow guard), negatives accepted. Table-driven.</t>
+        </is>
+      </c>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
@@ -6164,40 +6228,40 @@
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>T10-08.1</t>
+          <t>T10-07.7</t>
         </is>
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>core/deps.py + tenancy.py</t>
+          <t>services/ingestion.py</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>Formula/Edge</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>2-tenant cross-id read matrix</t>
+          <t>Duplicate exact-float equality</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>Create tenants A + B with overlapping data. B reads A's task/decision/workflow/invoice/contact/brain-doc by id -&gt; 404 (never data) across all 30 TENANT_COLLECTIONS.</t>
-        </is>
-      </c>
-      <c r="G84" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>iamt==camt exact == : test 0.1+0.2, OCR decimals that don't round-trip -&gt; dup MISSED. Assert the fragility.</t>
+        </is>
+      </c>
+      <c r="G84" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -6220,35 +6284,35 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>T10-08.2</t>
+          <t>T10-07.8</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>services/tenancy.py</t>
+          <t>services/ingestion.py</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>Formula/Edge</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>2-tenant cross-id write matrix</t>
+          <t>Dup date-window boundaries</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>B PATCH/DELETE A's records by id -&gt; 404. ensure_owned raises 404 for both missing + wrong-tenant (no existence probing).</t>
-        </is>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>gap==7 (dup) vs gap==8 (not); unparseable date (gap None) -&gt; treated as dup; number-only pool capped 500 (dup beyond cap missed).</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
@@ -6276,35 +6340,35 @@
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>T10-08.3</t>
+          <t>T10-07.9</t>
         </is>
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t>core/deps.py</t>
+          <t>routers/ledger.py</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>Formula/Edge</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Legacy-token fallback probe</t>
+          <t>Payment-match ambiguity + smart-match</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>deps.py:107 trusts user.tenant_id==claimed + legacy role when no membership found. Probe this mid-migration escape hatch for privilege/tenant confusion.</t>
-        </is>
-      </c>
-      <c r="G86" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>2+ invoices with same normalized number -&gt; None (human review, no auto-match). Smart-match needs same contact + exact balance + within 30 days.</t>
+        </is>
+      </c>
+      <c r="G86" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
@@ -6332,40 +6396,40 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>T10-08.4</t>
+          <t>T10-07.10</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>routers/files.py</t>
+          <t>routers/ledger.py</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>Formula/Edge</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>File serve-by-name tenant scope</t>
+          <t>Settle epsilon 0.01</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>GET /files/{fname} searches files/ingestions/ledger-attachments/capture-drafts -&gt; must resolve ONLY caller's tenant. Path traversal (../) -&gt; 404. Legacy local-disk default off.</t>
-        </is>
-      </c>
-      <c r="G87" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>Invoice/payment settle at 0.01 tolerance: balances 0.005 (settled), 0.01 (settled), 0.011 (partial). Assert paid vs partial status transitions.</t>
+        </is>
+      </c>
+      <c r="G87" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -6388,40 +6452,40 @@
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>T10-08.5</t>
+          <t>T10-07.11</t>
         </is>
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>routers/whatsapp.py</t>
+          <t>services/finance_signals.py</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>Formula/Edge</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>WhatsApp log leak</t>
+          <t>Escalation ladder boundaries</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Unrouted events (tenant_id=None) must NOT surface to any tenant's /whatsapp/logs. Owner-only log read strictly tenant-scoped.</t>
-        </is>
-      </c>
-      <c r="G88" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>days=(now-due).days: &lt;1 L1 notify, &lt;2 L2, &lt;3 L3 manager, else L4 OWNER ALERT. Monotonic/idempotent (skip if target&lt;=stored). Test each boundary day.</t>
+        </is>
+      </c>
+      <c r="G88" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -6444,30 +6508,30 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>T10-08.6</t>
+          <t>T10-07.12</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>routers/brain_docs.py</t>
+          <t>services/captures.py</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>Formula/Edge</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Brain doc visibility matrix</t>
+          <t>Capture 50000 + text/voice never-auto</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>public/dept/private/roles_allowed/uploader/owner on get/download/edit/delete; file_open re-checks per-doc visibility. A user can't open a doc they can't see.</t>
+          <t>needs_owner at amount&gt;=50000; auto-file requires &lt;50000 strict AND is_document -&gt; 50000 never auto-files AND text/voice (is_document=False) can never auto-file even at low value.</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
@@ -6477,7 +6541,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -6500,30 +6564,30 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>T10-08.7</t>
+          <t>T10-07.13</t>
         </is>
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>routers/auth_otp.py</t>
+          <t>routers/ledger.py</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>Formula/Edge</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>OTP/WhatsApp routing tenant-scoped</t>
+          <t>net_profit + mixed currency</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>otp_codes keyed by (phone,tenant); multi-tenant OTP request returns no code + no workspace-list leak; verify without hint -&gt; 409 ambiguous.</t>
+          <t>net_profit=revenue BILLED - ALL expenses (not cash). Mixed-currency invoices summed with NO FX conversion. Assert both quirks explicitly.</t>
         </is>
       </c>
       <c r="G90" s="13" t="inlineStr">
@@ -6533,7 +6597,7 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -6556,30 +6620,30 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>T10-08.8</t>
+          <t>T10-07.14</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>routers/admin.py</t>
+          <t>services/operating_score.py</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>Formula/Edge</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Tenant deletion completeness (live)</t>
+          <t>Malformed amount reaches score</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Extend the unit test to a live 2-tenant run: seed A in every collection, delete A, assert 0 rows remain for A AND B fully intact. Files wiped from obj_store.</t>
+          <t>A non-numeric amount string on an invoice hits float(i.get('amount') or 0) with NO try/except in operating_score -&gt; raises. Assert + harden.</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
@@ -6589,7 +6653,7 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -6612,12 +6676,12 @@
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>T10-08.9</t>
+          <t>T10-08.1</t>
         </is>
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>bootstrap/lifecycle.py</t>
+          <t>core/deps.py + tenancy.py</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
@@ -6630,22 +6694,22 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>Global email uniqueness behavior</t>
+          <t>2-tenant cross-id read matrix</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>Email unique across ALL tenants (legacy users index). Assert same email can't create a second tenant's legacy user; memberships model is (user_id,tenant_id) compound-unique.</t>
-        </is>
-      </c>
-      <c r="G92" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Create tenants A + B with overlapping data. B reads A's task/decision/workflow/invoice/contact/brain-doc by id -&gt; 404 (never data) across all 30 TENANT_COLLECTIONS.</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -6668,12 +6732,12 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>T10-08.10</t>
+          <t>T10-08.2</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>core/deps.py</t>
+          <t>services/tenancy.py</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
@@ -6686,17 +6750,17 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Session revoke + suspend gates</t>
+          <t>2-tenant cross-id write matrix</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>Logout blacklists jti (stale JWT -&gt; refused); membership removed mid-session -&gt; 403 next request; tenant/user suspend -&gt; 403 everywhere.</t>
-        </is>
-      </c>
-      <c r="G93" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>B PATCH/DELETE A's records by id -&gt; 404. ensure_owned raises 404 for both missing + wrong-tenant (no existence probing).</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
@@ -6724,35 +6788,35 @@
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>T10-09.1</t>
+          <t>T10-08.3</t>
         </is>
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>services/ingestion.py</t>
+          <t>core/deps.py</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>AI/Extraction</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>Invoice OCR clean extract</t>
+          <t>Legacy-token fallback probe</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>Feed a clean invoice image/PDF -&gt; correct amount/vendor/number/date/type. Assert calibrated confidence high -&gt; routes to auto/confirm not attention.</t>
-        </is>
-      </c>
-      <c r="G94" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>deps.py:107 trusts user.tenant_id==claimed + legacy role when no membership found. Probe this mid-migration escape hatch for privilege/tenant confusion.</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
@@ -6780,35 +6844,35 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>T10-09.2</t>
+          <t>T10-08.4</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>services/ingestion.py</t>
+          <t>routers/files.py</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>AI/Extraction</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Invoice OCR blurry/low-confidence</t>
+          <t>File serve-by-name tenant scope</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>Blurry/partial doc -&gt; low confidence -&gt; needs_review true -&gt; attention queue. Assert it never silently auto-files.</t>
-        </is>
-      </c>
-      <c r="G95" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>GET /files/{fname} searches files/ingestions/ledger-attachments/capture-drafts -&gt; must resolve ONLY caller's tenant. Path traversal (../) -&gt; 404. Legacy local-disk default off.</t>
+        </is>
+      </c>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
@@ -6836,40 +6900,40 @@
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>T10-09.3</t>
+          <t>T10-08.5</t>
         </is>
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>services/ingestion.py</t>
+          <t>routers/whatsapp.py</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>AI/Extraction</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>Invoice foreign / missing fields</t>
+          <t>WhatsApp log leak</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>Non-English or missing-number/date invoice -&gt; graceful extraction, no crash, unknowns flagged, human-review routed.</t>
-        </is>
-      </c>
-      <c r="G96" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Unrouted events (tenant_id=None) must NOT surface to any tenant's /whatsapp/logs. Owner-only log read strictly tenant-scoped.</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -6892,35 +6956,35 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>T10-09.4</t>
+          <t>T10-08.6</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>services/ingestion.py</t>
+          <t>routers/brain_docs.py</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>AI/Extraction</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>CSV/Excel multi-sheet mapping</t>
+          <t>Brain doc visibility matrix</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>ai_map_spreadsheet on a messy multi-sheet workbook -&gt; correct column-&gt;field mapping, per-row records, review before commit.</t>
-        </is>
-      </c>
-      <c r="G97" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>public/dept/private/roles_allowed/uploader/owner on get/download/edit/delete; file_open re-checks per-doc visibility. A user can't open a doc they can't see.</t>
+        </is>
+      </c>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
@@ -6948,35 +7012,35 @@
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>T10-09.5</t>
+          <t>T10-08.7</t>
         </is>
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>integrations/stt + services/voice.py</t>
+          <t>routers/auth_otp.py</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>AI/Extraction</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>Voice-&gt;task Tanglish/codemix</t>
+          <t>OTP/WhatsApp routing tenant-scoped</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>Sarvam codemix (Tanglish) audio -&gt; transcription -&gt; decision + tasks. The India-primary voice path (see Sarvam ref).</t>
-        </is>
-      </c>
-      <c r="G98" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>otp_codes keyed by (phone,tenant); multi-tenant OTP request returns no code + no workspace-list leak; verify without hint -&gt; 409 ambiguous.</t>
+        </is>
+      </c>
+      <c r="G98" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
@@ -7004,35 +7068,35 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>T10-09.6</t>
+          <t>T10-08.8</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>services/voice.py</t>
+          <t>routers/admin.py</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>AI/Extraction</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Voice noisy / accented resilience</t>
+          <t>Tenant deletion completeness (live)</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>Noisy or heavily-accented audio -&gt; transcription + extraction degrade gracefully, STT-fail -&gt; 503, no partial garbage decision.</t>
-        </is>
-      </c>
-      <c r="G99" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Extend the unit test to a live 2-tenant run: seed A in every collection, delete A, assert 0 rows remain for A AND B fully intact. Files wiped from obj_store.</t>
+        </is>
+      </c>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
@@ -7060,40 +7124,40 @@
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>T10-09.7</t>
+          <t>T10-08.9</t>
         </is>
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>services/captures.py</t>
+          <t>bootstrap/lifecycle.py</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>AI/Extraction</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Capture triage precision</t>
+          <t>Global email uniqueness behavior</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
         <is>
-          <t>ai_capture_triage classifies + routes; fewer false 'unrelated'; classification not in CAPTURE_CLASSES -&gt; 'other'; confidence default 0.7 on bad.</t>
-        </is>
-      </c>
-      <c r="G100" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Email unique across ALL tenants (legacy users index). Assert same email can't create a second tenant's legacy user; memberships model is (user_id,tenant_id) compound-unique.</t>
+        </is>
+      </c>
+      <c r="G100" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -7116,35 +7180,35 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>T10-09.8</t>
+          <t>T10-08.10</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>routers/brain.py</t>
+          <t>core/deps.py</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>AI/Extraction</t>
+          <t>Isolation</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Dex RAG citation accuracy</t>
+          <t>Session revoke + suspend gates</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>Ask a question answerable only from an uploaded doc -&gt; answer cites brain_documents; provenance from brain_context. Wrong/absent citation is a fail.</t>
-        </is>
-      </c>
-      <c r="G101" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Logout blacklists jti (stale JWT -&gt; refused); membership removed mid-session -&gt; 403 next request; tenant/user suspend -&gt; 403 everywhere.</t>
+        </is>
+      </c>
+      <c r="G101" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
@@ -7172,12 +7236,12 @@
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>T10-09.9</t>
+          <t>T10-09.1</t>
         </is>
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>routers/brain.py + brain_router.py</t>
+          <t>services/ingestion.py</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
@@ -7190,17 +7254,17 @@
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>Brain RBAC intent gate</t>
+          <t>Invoice OCR clean extract</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>non-finance 'what are our sales?' -&gt; PERMISSION_DENIED (stricter of LLM-classified vs regex intent). Finance columns stripped even if rows retrieved.</t>
-        </is>
-      </c>
-      <c r="G102" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>Feed a clean invoice image/PDF -&gt; correct amount/vendor/number/date/type. Assert calibrated confidence high -&gt; routes to auto/confirm not attention.</t>
+        </is>
+      </c>
+      <c r="G102" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H102" s="11" t="inlineStr">
@@ -7228,12 +7292,12 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>T10-09.10</t>
+          <t>T10-09.2</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>services/captures.py</t>
+          <t>services/ingestion.py</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
@@ -7246,17 +7310,17 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Prompt-injection / jailbreak defense</t>
+          <t>Invoice OCR blurry/low-confidence</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>Malicious instructions inside a WhatsApp/voice message (wrapped as untrusted) must not execute; assert the injection-defense guard holds.</t>
-        </is>
-      </c>
-      <c r="G103" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Blurry/partial doc -&gt; low confidence -&gt; needs_review true -&gt; attention queue. Assert it never silently auto-files.</t>
+        </is>
+      </c>
+      <c r="G103" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
@@ -7284,12 +7348,12 @@
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>T10-09.11</t>
+          <t>T10-09.3</t>
         </is>
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>cross-cutting AI</t>
+          <t>services/ingestion.py</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
@@ -7302,17 +7366,17 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>AI fail-open contract</t>
+          <t>Invoice foreign / missing fields</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>Every LLM call: on error/timeout falls back to template/typed values and NEVER breaks the request. Kill the LLM mid-call, assert 200 with fallback.</t>
-        </is>
-      </c>
-      <c r="G104" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Non-English or missing-number/date invoice -&gt; graceful extraction, no crash, unknowns flagged, human-review routed.</t>
+        </is>
+      </c>
+      <c r="G104" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
@@ -7340,12 +7404,12 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>T10-09.12</t>
+          <t>T10-09.4</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>services/ai/validation.py</t>
+          <t>services/ingestion.py</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
@@ -7358,12 +7422,12 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Confidence -&gt; routing correctness</t>
+          <t>CSV/Excel multi-sheet mapping</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>Calibrated confidence drives auto/confirm/attention. Assert the full mapping: parse-fail/no-records/low-conf all land in the right queue.</t>
+          <t>ai_map_spreadsheet on a messy multi-sheet workbook -&gt; correct column-&gt;field mapping, per-row records, review before commit.</t>
         </is>
       </c>
       <c r="G105" s="15" t="inlineStr">
@@ -7373,7 +7437,7 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
@@ -7396,35 +7460,35 @@
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>T10-10.1</t>
+          <t>T10-09.5</t>
         </is>
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>services/workflow_engine.py</t>
+          <t>integrations/stt + services/voice.py</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>AI/Extraction</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>Parallel workflow advance (CAS)</t>
+          <t>Voice-&gt;task Tanglish/codemix</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>N concurrent advance() on ONE workflow -&gt; exactly ONE transition (WE-09 stage_version CAS); losers get already_advanced=True. Prove the single-writer contract at runtime.</t>
-        </is>
-      </c>
-      <c r="G106" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Sarvam codemix (Tanglish) audio -&gt; transcription -&gt; decision + tasks. The India-primary voice path (see Sarvam ref).</t>
+        </is>
+      </c>
+      <c r="G106" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H106" s="11" t="inlineStr">
@@ -7452,40 +7516,40 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>T10-10.2</t>
+          <t>T10-09.6</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>routers/ledger.py</t>
+          <t>services/voice.py</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>AI/Extraction</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Parallel payment matching (EXPOSE bug)</t>
+          <t>Voice noisy / accented resilience</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>2+ payments reconciling the SAME invoice concurrently -&gt; _apply_payment_to_invoice is read-modify-write with NO version guard -&gt; lost update / double-allocation / wrong paid-vs-partial. Highest-value concurrency test.</t>
-        </is>
-      </c>
-      <c r="G107" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>Noisy or heavily-accented audio -&gt; transcription + extraction degrade gracefully, STT-fail -&gt; 503, no partial garbage decision.</t>
+        </is>
+      </c>
+      <c r="G107" s="16" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
@@ -7508,35 +7572,35 @@
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>T10-10.3</t>
+          <t>T10-09.7</t>
         </is>
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>services/plans.py + team.py</t>
+          <t>services/captures.py</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>AI/Extraction</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>Seat-limit TOCTOU</t>
+          <t>Capture triage precision</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>N parallel invites at cap boundary -&gt; count-then-insert with no atomic reservation -&gt; all pass -&gt; over-provision. Expose + propose an atomic reservation fix.</t>
-        </is>
-      </c>
-      <c r="G108" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>ai_capture_triage classifies + routes; fewer false 'unrelated'; classification not in CAPTURE_CLASSES -&gt; 'other'; confidence default 0.7 on bad.</t>
+        </is>
+      </c>
+      <c r="G108" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
@@ -7564,35 +7628,35 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>T10-10.4</t>
+          <t>T10-09.8</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>services/workflow_engine.py</t>
+          <t>routers/brain.py</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>AI/Extraction</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Stage-enter double-spawn</t>
+          <t>Dex RAG citation accuracy</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>on_stage_enter is find-then-insert with NO unique index -&gt; concurrent re-entry (advance racing a retry) double-spawns template tasks. Expose the duplicate.</t>
-        </is>
-      </c>
-      <c r="G109" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Ask a question answerable only from an uploaded doc -&gt; answer cites brain_documents; provenance from brain_context. Wrong/absent citation is a fail.</t>
+        </is>
+      </c>
+      <c r="G109" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
@@ -7620,35 +7684,35 @@
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>T10-10.5</t>
+          <t>T10-09.9</t>
         </is>
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>services/quotas.py</t>
+          <t>routers/brain.py + brain_router.py</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>AI/Extraction</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>Quota overshoot under parallel AI</t>
+          <t>Brain RBAC intent gate</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>check_quota reads a monthly aggregate + fail-open with no reservation -&gt; N parallel AI calls collectively exceed cap before the aggregate catches up. Measure overshoot.</t>
-        </is>
-      </c>
-      <c r="G110" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>non-finance 'what are our sales?' -&gt; PERMISSION_DENIED (stricter of LLM-classified vs regex intent). Finance columns stripped even if rows retrieved.</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
@@ -7676,30 +7740,30 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>T10-10.6</t>
+          <t>T10-09.10</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>services/leader_lock.py</t>
+          <t>services/captures.py</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>AI/Extraction</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Scheduler leader-lock (multi-replica)</t>
+          <t>Prompt-injection / jailbreak defense</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>3 replicas tick simultaneously -&gt; only the lock holder sweeps; no duplicate escalation emails/alerts. TTL crash-recovery hands over cleanly.</t>
+          <t>Malicious instructions inside a WhatsApp/voice message (wrapped as untrusted) must not execute; assert the injection-defense guard holds.</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
@@ -7732,35 +7796,35 @@
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>T10-10.7</t>
+          <t>T10-09.11</t>
         </is>
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>services/finance_signals.py</t>
+          <t>cross-cutting AI</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>AI/Extraction</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>Follow-up throttle behavior</t>
+          <t>AI fail-open contract</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>60s per-tenant in-memory throttle resets on restart + is NOT shared across workers -&gt; multi-worker can double-run a sweep. Assert the gap + idempotency guards absorb it.</t>
-        </is>
-      </c>
-      <c r="G112" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Every LLM call: on error/timeout falls back to template/typed values and NEVER breaks the request. Kill the LLM mid-call, assert 200 with fallback.</t>
+        </is>
+      </c>
+      <c r="G112" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
@@ -7788,30 +7852,30 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>T10-10.8</t>
+          <t>T10-09.12</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>routers/tasks.py</t>
+          <t>services/ai/validation.py</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>AI/Extraction</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Auto-invoice idempotency race</t>
+          <t>Confidence -&gt; routing correctness</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>Completing an invoice-titled task twice concurrently -&gt; exactly one draft invoice (source_task_id guard). No duplicate.</t>
+          <t>Calibrated confidence drives auto/confirm/attention. Assert the full mapping: parse-fail/no-records/low-conf all land in the right queue.</t>
         </is>
       </c>
       <c r="G113" s="15" t="inlineStr">
@@ -7844,12 +7908,12 @@
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>T10-10.9</t>
+          <t>T10-10.1</t>
         </is>
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>routers/ledger.py</t>
+          <t>services/workflow_engine.py</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
@@ -7862,22 +7926,22 @@
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>Standalone-payment expense idempotency</t>
+          <t>Parallel workflow advance (CAS)</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>Two concurrent standalone out-payments with same payment_id -&gt; exactly one booked expense (payment_id dedup).</t>
-        </is>
-      </c>
-      <c r="G114" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>N concurrent advance() on ONE workflow -&gt; exactly ONE transition (WE-09 stage_version CAS); losers get already_advanced=True. Prove the single-writer contract at runtime.</t>
+        </is>
+      </c>
+      <c r="G114" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -7900,12 +7964,12 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>T10-10.10</t>
+          <t>T10-10.2</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>bootstrap/lifecycle.py</t>
+          <t>routers/ledger.py</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
@@ -7918,22 +7982,22 @@
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Billing webhook idempotency</t>
+          <t>Parallel payment matching (EXPOSE bug)</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>Duplicate Razorpay webhook (same idempotency_key) -&gt; unique index blocks double-charge/double-upgrade. Fire the same event twice.</t>
-        </is>
-      </c>
-      <c r="G115" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>2+ payments reconciling the SAME invoice concurrently -&gt; _apply_payment_to_invoice is read-modify-write with NO version guard -&gt; lost update / double-allocation / wrong paid-vs-partial. Highest-value concurrency test.</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
@@ -7956,30 +8020,30 @@
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>T10-11.1</t>
+          <t>T10-10.3</t>
         </is>
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>tests/conftest.py (new)</t>
+          <t>services/plans.py + team.py</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>Seeded / isolated test DB</t>
+          <t>Seat-limit TOCTOU</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>Stop integration tests mutating the shared hosted dev DB. Stand up a disposable test Mongo (or per-run tenant namespace) seeded fresh. Root cause of current flaky iteration_* failures.</t>
+          <t>N parallel invites at cap boundary -&gt; count-then-insert with no atomic reservation -&gt; all pass -&gt; over-provision. Expose + propose an atomic reservation fix.</t>
         </is>
       </c>
       <c r="G116" s="14" t="inlineStr">
@@ -7989,7 +8053,7 @@
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
@@ -8012,40 +8076,40 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>T10-11.2</t>
+          <t>T10-10.4</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>tests/</t>
+          <t>services/workflow_engine.py</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Fix pre-existing iteration_* failures</t>
+          <t>Stage-enter double-spawn</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>The iteration_* suite fails against shared-DB state (e.g. 11 in test_iteration60_admin). Once on an isolated DB, fix the real assertions so the suite is green.</t>
-        </is>
-      </c>
-      <c r="G117" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>on_stage_enter is find-then-insert with NO unique index -&gt; concurrent re-entry (advance racing a retry) double-spawns template tasks. Expose the duplicate.</t>
+        </is>
+      </c>
+      <c r="G117" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
@@ -8068,35 +8132,35 @@
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>T10-11.3</t>
+          <t>T10-10.5</t>
         </is>
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>tests/conftest.py</t>
+          <t>services/quotas.py</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>conftest + shared fixtures</t>
+          <t>Quota overshoot under parallel AI</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>No conftest.py today. Add fixtures: per-test tenant, authed clients per role, factory-seeded businesses, teardown. Cuts boilerplate across 125 files.</t>
-        </is>
-      </c>
-      <c r="G118" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>check_quota reads a monthly aggregate + fail-open with no reservation -&gt; N parallel AI calls collectively exceed cap before the aggregate catches up. Measure overshoot.</t>
+        </is>
+      </c>
+      <c r="G118" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr">
@@ -8124,35 +8188,35 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>T10-11.4</t>
+          <t>T10-10.6</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>services/leader_lock.py</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>CI regression gate</t>
+          <t>Scheduler leader-lock (multi-replica)</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>Build+test pipeline gated on the suite. Split unit (offline, always) vs integration (needs backend). Block merge on unit-suite red. (Ties to Epic 1 S5-06 CI/CD.)</t>
-        </is>
-      </c>
-      <c r="G119" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>3 replicas tick simultaneously -&gt; only the lock holder sweeps; no duplicate escalation emails/alerts. TTL crash-recovery hands over cleanly.</t>
+        </is>
+      </c>
+      <c r="G119" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
@@ -8180,40 +8244,40 @@
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>T10-11.5</t>
+          <t>T10-10.7</t>
         </is>
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>tests/</t>
+          <t>services/finance_signals.py</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>Unit vs integration markers</t>
+          <t>Follow-up throttle behavior</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>Mark the ~70 offline-unit vs ~55 live-integration files (pytest markers). CI runs unit on every PR; integration on a staged env.</t>
-        </is>
-      </c>
-      <c r="G120" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>60s per-tenant in-memory throttle resets on restart + is NOT shared across workers -&gt; multi-worker can double-run a sweep. Assert the gap + idempotency guards absorb it.</t>
+        </is>
+      </c>
+      <c r="G120" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
@@ -8236,40 +8300,40 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>T10-11.6</t>
+          <t>T10-10.8</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>tests/</t>
+          <t>routers/tasks.py</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>Multi-tenant leakage API test (the big gap)</t>
+          <t>Auto-invoice idempotency race</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>No test creates 2 LIVE tenants + asserts cross-id 404 at the API layer. Build it (this is Sprint 8 automated) -&gt; the single most valuable missing test.</t>
-        </is>
-      </c>
-      <c r="G121" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>Completing an invoice-titled task twice concurrently -&gt; exactly one draft invoice (source_task_id guard). No duplicate.</t>
+        </is>
+      </c>
+      <c r="G121" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -8292,40 +8356,40 @@
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>T10-11.7</t>
+          <t>T10-10.9</t>
         </is>
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>routers/ledger.py</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="E122" s="12" t="inlineStr">
         <is>
-          <t>Coverage report + targets</t>
+          <t>Standalone-payment expense idempotency</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>Wire coverage measurement; set a floor on the high-risk modules (operating_score, ledger, ingestion, permissions, tenancy). Track % per sprint.</t>
-        </is>
-      </c>
-      <c r="G122" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Two concurrent standalone out-payments with same payment_id -&gt; exactly one booked expense (payment_id dedup).</t>
+        </is>
+      </c>
+      <c r="G122" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
@@ -8348,30 +8412,30 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>T10-11.8</t>
+          <t>T10-10.10</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>tests/</t>
+          <t>bootstrap/lifecycle.py</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>Flaky-test triage</t>
+          <t>Billing webhook idempotency</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>Catalogue the environmental failures; make each deterministic (isolated data, no wall-clock/order dependence). Zero-flake target.</t>
+          <t>Duplicate Razorpay webhook (same idempotency_key) -&gt; unique index blocks double-charge/double-upgrade. Fire the same event twice.</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
@@ -8381,7 +8445,7 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
@@ -8404,12 +8468,12 @@
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>T10-11.9</t>
+          <t>T10-11.1</t>
         </is>
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>tests/factories (new)</t>
+          <t>tests/conftest.py (new)</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
@@ -8422,22 +8486,22 @@
       </c>
       <c r="E124" s="12" t="inlineStr">
         <is>
-          <t>Test-data factory for niches</t>
+          <t>Seeded / isolated test DB</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>Reusable generators: build a realistic tenant per industry (textile/logistics/restaurant/...) with contacts/invoices/tasks. Powers Sprint 5 + 6.</t>
-        </is>
-      </c>
-      <c r="G124" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Stop integration tests mutating the shared hosted dev DB. Stand up a disposable test Mongo (or per-run tenant namespace) seeded fresh. Root cause of current flaky iteration_* failures.</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -8460,12 +8524,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>T10-11.10</t>
+          <t>T10-11.2</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>tests/</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
@@ -8478,22 +8542,22 @@
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Post-sprint regression baseline</t>
+          <t>Fix pre-existing iteration_* failures</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>Full suite re-run after each sprint merges to Backend_optimization; baseline must stay green (the Epic-1 Testing-Plan phase-A regression discipline, automated).</t>
-        </is>
-      </c>
-      <c r="G125" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>The iteration_* suite fails against shared-DB state (e.g. 11 in test_iteration60_admin). Once on an isolated DB, fix the real assertions so the suite is green.</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
@@ -8516,40 +8580,40 @@
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>T10-12.1</t>
+          <t>T10-11.3</t>
         </is>
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>tests/conftest.py</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
         <is>
-          <t>Owner golden path</t>
+          <t>conftest + shared fixtures</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>signup -&gt; onboard -&gt; create decision -&gt; approve -&gt; task done (with evidence) -&gt; invoice raised -&gt; payment matched -&gt; operating score reflects. One unbroken owner journey.</t>
-        </is>
-      </c>
-      <c r="G126" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>No conftest.py today. Add fixtures: per-test tenant, authed clients per role, factory-seeded businesses, teardown. Cuts boilerplate across 125 files.</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
@@ -8572,35 +8636,35 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>T10-12.2</t>
+          <t>T10-11.4</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>Finance persona journey</t>
+          <t>CI regression gate</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>Login finance -&gt; ingest bills -&gt; classify expense/asset/inventory -&gt; match inbound payments -&gt; outstanding correct -&gt; AI finance brief. Money surfaces only where finance-permitted.</t>
-        </is>
-      </c>
-      <c r="G127" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Build+test pipeline gated on the suite. Split unit (offline, always) vs integration (needs backend). Block merge on unit-suite red. (Ties to Epic 1 S5-06 CI/CD.)</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
@@ -8628,30 +8692,30 @@
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>T10-12.3</t>
+          <t>T10-11.5</t>
         </is>
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>tests/</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>Sales persona journey</t>
+          <t>Unit vs integration markers</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>Login sales -&gt; add contact -&gt; log activity -&gt; CRM outstanding -&gt; raise a complaint -&gt; resolve -&gt; brain_context written. Blocked from finance detail.</t>
+          <t>Mark the ~70 offline-unit vs ~55 live-integration files (pytest markers). CI runs unit on every PR; integration on a staged env.</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
@@ -8661,7 +8725,7 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
@@ -8684,35 +8748,35 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>T10-12.4</t>
+          <t>T10-11.6</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>tests/</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Operations persona journey</t>
+          <t>Multi-tenant leakage API test (the big gap)</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>Login operations -&gt; tasks -&gt; start workflow -&gt; advance stages -&gt; request leave -&gt; (owner) approve -&gt; calendar reflects. Exercises the ops-role perm gap.</t>
-        </is>
-      </c>
-      <c r="G129" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>No test creates 2 LIVE tenants + asserts cross-id 404 at the API layer. Build it (this is Sprint 8 automated) -&gt; the single most valuable missing test.</t>
+        </is>
+      </c>
+      <c r="G129" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
@@ -8740,30 +8804,30 @@
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>T10-12.5</t>
+          <t>T10-11.7</t>
         </is>
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>Multi-role parallel day</t>
+          <t>Coverage report + targets</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>owner+finance+sales+ops all active same tenant same window -&gt; cross-module consistency (a decision's tasks, an invoice's payment, a workflow's stage) with no contention corruption.</t>
+          <t>Wire coverage measurement; set a floor on the high-risk modules (operating_score, ledger, ingestion, permissions, tenancy). Track % per sprint.</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
@@ -8773,7 +8837,7 @@
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
@@ -8796,35 +8860,35 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>T10-12.6</t>
+          <t>T10-11.8</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>tests/</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>WhatsApp -&gt; action E2E</t>
+          <t>Flaky-test triage</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>Send a bill photo to the WhatsApp number -&gt; capture draft -&gt; owner approves -&gt; ledger record created + inbox closed. The zero-typing capture path.</t>
-        </is>
-      </c>
-      <c r="G131" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Catalogue the environmental failures; make each deterministic (isolated data, no wall-clock/order dependence). Zero-flake target.</t>
+        </is>
+      </c>
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
@@ -8852,35 +8916,35 @@
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>T10-12.7</t>
+          <t>T10-11.9</t>
         </is>
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>tests/factories (new)</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>Voice -&gt; decision -&gt; execution E2E</t>
+          <t>Test-data factory for niches</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>Dictate a directive -&gt; Dex structures pending_approval decision + blocked tasks -&gt; approve -&gt; generate execution plan -&gt; tick steps -&gt; complete. The flagship voice loop.</t>
-        </is>
-      </c>
-      <c r="G132" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Reusable generators: build a realistic tenant per industry (textile/logistics/restaurant/...) with contacts/invoices/tasks. Powers Sprint 5 + 6.</t>
+        </is>
+      </c>
+      <c r="G132" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H132" s="11" t="inlineStr">
@@ -8908,40 +8972,40 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>T10-12.8</t>
+          <t>T10-11.10</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>scripts/we15_golden_path_kapoor.py</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>Kapoor golden-path (extend)</t>
+          <t>Post-sprint regression baseline</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>Take the existing we15 Kapoor script from smoke to full assertion: every stage, every role hand-off, final outstanding + operating score verified.</t>
-        </is>
-      </c>
-      <c r="G133" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Full suite re-run after each sprint merges to Backend_optimization; baseline must stay green (the Epic-1 Testing-Plan phase-A regression discipline, automated).</t>
+        </is>
+      </c>
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
@@ -8964,12 +9028,12 @@
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>T10-12.9</t>
+          <t>T10-12.1</t>
         </is>
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t>docs Testing Plan</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
@@ -8982,12 +9046,12 @@
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>Phase A-J exit-criteria gate</t>
+          <t>Owner golden path</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>Map each Testing-Plan phase (A automated ... J GA) to a concrete pass/fail gate in this epic. Assert entry-&gt;exit criteria are met before advancing rollout stage.</t>
+          <t>signup -&gt; onboard -&gt; create decision -&gt; approve -&gt; task done (with evidence) -&gt; invoice raised -&gt; payment matched -&gt; operating score reflects. One unbroken owner journey.</t>
         </is>
       </c>
       <c r="G134" s="13" t="inlineStr">
@@ -8997,7 +9061,7 @@
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -9020,12 +9084,12 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>T10-12.10</t>
+          <t>T10-12.2</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>docs Go-Live Checklist</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
@@ -9038,17 +9102,17 @@
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Go-live testing sign-off</t>
+          <t>Finance persona journey</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>Every testing dimension (S1-S11) green -&gt; flip the Testing rows on the Go-Live Checklist. The formal QA sign-off before self-serve signup opens. (Runs with Epic 1 S5.)</t>
-        </is>
-      </c>
-      <c r="G135" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>Login finance -&gt; ingest bills -&gt; classify expense/asset/inventory -&gt; match inbound payments -&gt; outstanding correct -&gt; AI finance brief. Money surfaces only where finance-permitted.</t>
+        </is>
+      </c>
+      <c r="G135" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
@@ -9068,6 +9132,1126 @@
         </is>
       </c>
       <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>T10-12.3</t>
+        </is>
+      </c>
+      <c r="B136" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>Sales persona journey</t>
+        </is>
+      </c>
+      <c r="F136" s="12" t="inlineStr">
+        <is>
+          <t>Login sales -&gt; add contact -&gt; log activity -&gt; CRM outstanding -&gt; raise a complaint -&gt; resolve -&gt; brain_context written. Blocked from finance detail.</t>
+        </is>
+      </c>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="n"/>
+      <c r="K136" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L136" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>T10-12.4</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>Operations persona journey</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
+        <is>
+          <t>Login operations -&gt; tasks -&gt; start workflow -&gt; advance stages -&gt; request leave -&gt; (owner) approve -&gt; calendar reflects. Exercises the ops-role perm gap.</t>
+        </is>
+      </c>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="n"/>
+      <c r="K137" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L137" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>T10-12.5</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>Multi-role parallel day</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="inlineStr">
+        <is>
+          <t>owner+finance+sales+ops all active same tenant same window -&gt; cross-module consistency (a decision's tasks, an invoice's payment, a workflow's stage) with no contention corruption.</t>
+        </is>
+      </c>
+      <c r="G138" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="n"/>
+      <c r="K138" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L138" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>T10-12.6</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>WhatsApp -&gt; action E2E</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="inlineStr">
+        <is>
+          <t>Send a bill photo to the WhatsApp number -&gt; capture draft -&gt; owner approves -&gt; ledger record created + inbox closed. The zero-typing capture path.</t>
+        </is>
+      </c>
+      <c r="G139" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="n"/>
+      <c r="K139" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>T10-12.7</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>Voice -&gt; decision -&gt; execution E2E</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="inlineStr">
+        <is>
+          <t>Dictate a directive -&gt; Dex structures pending_approval decision + blocked tasks -&gt; approve -&gt; generate execution plan -&gt; tick steps -&gt; complete. The flagship voice loop.</t>
+        </is>
+      </c>
+      <c r="G140" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="n"/>
+      <c r="K140" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L140" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>T10-12.8</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>scripts/we15_golden_path_kapoor.py</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Kapoor golden-path (extend)</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>Take the existing we15 Kapoor script from smoke to full assertion: every stage, every role hand-off, final outstanding + operating score verified.</t>
+        </is>
+      </c>
+      <c r="G141" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H141" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I141" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J141" s="11" t="n"/>
+      <c r="K141" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L141" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>T10-12.9</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>docs Testing Plan</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>Phase A-J exit-criteria gate</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="inlineStr">
+        <is>
+          <t>Map each Testing-Plan phase (A automated ... J GA) to a concrete pass/fail gate in this epic. Assert entry-&gt;exit criteria are met before advancing rollout stage.</t>
+        </is>
+      </c>
+      <c r="G142" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H142" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J142" s="11" t="n"/>
+      <c r="K142" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L142" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>T10-12.10</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>docs Go-Live Checklist</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>Go-live testing sign-off</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr">
+        <is>
+          <t>Every testing dimension (S1-S12) green -&gt; flip the Testing rows on the Go-Live Checklist. The formal QA sign-off before self-serve signup opens. (Runs with Epic 1 S5.)</t>
+        </is>
+      </c>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I143" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J143" s="11" t="n"/>
+      <c r="K143" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.1</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>BROWSER preview</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>Buttons &amp; controls sweep</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>Every primary/secondary/danger action across all pages does what its label says. No dead buttons, correct disabled + loading states, confirm dialogs on destructive actions name the blast radius. Driven in the browser preview (click -&gt; assert on-screen + backend effect).</t>
+        </is>
+      </c>
+      <c r="G144" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H144" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J144" s="11" t="n"/>
+      <c r="K144" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L144" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.2</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t>BROWSER preview</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Forms &amp; validation UX</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr">
+        <is>
+          <t>Required fields, inline error messages that name what to fix (not just 'invalid'), submit disabled until valid, success toasts, no silent failures. Across signup, task/decision/contact/finance/settings forms.</t>
+        </is>
+      </c>
+      <c r="G145" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="n"/>
+      <c r="K145" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.3</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
+          <t>BROWSER preview</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>Navigation &amp; routing</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="inlineStr">
+        <is>
+          <t>Every nav item + deep link + browser back/forward + redirects (/contacts-&gt;/crm, /brief-&gt;/inbox, etc.). No broken routes, no white screens; role-gated tabs shown/hidden correctly.</t>
+        </is>
+      </c>
+      <c r="G146" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H146" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J146" s="11" t="n"/>
+      <c r="K146" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L146" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.4</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t>BROWSER preview</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>Empty / loading / error states</t>
+        </is>
+      </c>
+      <c r="F147" s="12" t="inlineStr">
+        <is>
+          <t>Every list/panel/table has a real empty state (never a bare 'nothing'), skeletons that match final shape, and actionable error states. FE mirror of Epic 6 S15; checked visually in-browser.</t>
+        </is>
+      </c>
+      <c r="G147" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H147" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J147" s="11" t="n"/>
+      <c r="K147" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.5</t>
+        </is>
+      </c>
+      <c r="B148" s="12" t="inlineStr">
+        <is>
+          <t>resize_window</t>
+        </is>
+      </c>
+      <c r="C148" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>Responsive / mobile</t>
+        </is>
+      </c>
+      <c r="F148" s="12" t="inlineStr">
+        <is>
+          <t>375 (mobile) / 768 (tablet) / 1280 (desktop): no horizontal overflow, dock nav works, touch targets &gt;=44px, mobile-specific screens (karma mobile pass) render. Reload after resize so device gates re-run.</t>
+        </is>
+      </c>
+      <c r="G148" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H148" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I148" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J148" s="11" t="n"/>
+      <c r="K148" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L148" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.6</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t>BROWSER preview</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>Role-based UI (FE mirror of S3)</t>
+        </is>
+      </c>
+      <c r="F149" s="12" t="inlineStr">
+        <is>
+          <t>Log in as owner/finance/sales/operations -&gt; each sees ONLY its permitted tabs + actions; money surfaces hidden for non-finance; owner-only controls absent for members. The UI must match the backend RBAC, not just the API.</t>
+        </is>
+      </c>
+      <c r="G149" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H149" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I149" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J149" s="11" t="n"/>
+      <c r="K149" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L149" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.7</t>
+        </is>
+      </c>
+      <c r="B150" s="12" t="inlineStr">
+        <is>
+          <t>BROWSER preview</t>
+        </is>
+      </c>
+      <c r="C150" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="inlineStr">
+        <is>
+          <t>Karma design-system consistency</t>
+        </is>
+      </c>
+      <c r="F150" s="12" t="inlineStr">
+        <is>
+          <t>Post-karma-merge: one action colour (indigo), flat surfaces, serif display headings, consistent chip/pill/card patterns across every page. No leftover brutalist styling (except the deliberately-deferred admin theme).</t>
+        </is>
+      </c>
+      <c r="G150" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H150" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J150" s="11" t="n"/>
+      <c r="K150" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L150" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.8</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t>BROWSER preview</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="inlineStr">
+        <is>
+          <t>Browser-driven E2E per persona</t>
+        </is>
+      </c>
+      <c r="F151" s="12" t="inlineStr">
+        <is>
+          <t>Drive owner/finance/sales/ops journeys through the REAL UI (not the API): create a decision, approve it, log a payment, add a contact, dictate a note -&gt; assert the on-screen result each time. The FE counterpart of S12.</t>
+        </is>
+      </c>
+      <c r="G151" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H151" s="11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I151" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J151" s="11" t="n"/>
+      <c r="K151" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L151" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.9</t>
+        </is>
+      </c>
+      <c r="B152" s="12" t="inlineStr">
+        <is>
+          <t>BROWSER preview</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>Voice / Dex UI surfaces</t>
+        </is>
+      </c>
+      <c r="F152" s="12" t="inlineStr">
+        <is>
+          <t>Capture bar, the 'Dex is structuring N' inflight badge, the bottom-bar Dex + ribbon wave, the decision-review dialog, voice record/stop. Assert the async pipeline states surface correctly in the UI.</t>
+        </is>
+      </c>
+      <c r="G152" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H152" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J152" s="11" t="n"/>
+      <c r="K152" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L152" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.10</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>read_console + read_network</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>Console &amp; network health</t>
+        </is>
+      </c>
+      <c r="F153" s="12" t="inlineStr">
+        <is>
+          <t>No uncaught console errors, no failed API calls, no CORS errors on any main flow. Sweep every primary screen in the browser preview and assert a clean console + network tab.</t>
+        </is>
+      </c>
+      <c r="G153" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I153" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J153" s="11" t="n"/>
+      <c r="K153" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L153" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.11</t>
+        </is>
+      </c>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t>resize_window colorScheme</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>Theme + cross-surface render</t>
+        </is>
+      </c>
+      <c r="F154" s="12" t="inlineStr">
+        <is>
+          <t>Light/dark theme correctness; key flows render in the in-app browser pane; no theme-only unreadable text. Toggle and re-check the main surfaces.</t>
+        </is>
+      </c>
+      <c r="G154" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H154" s="11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J154" s="11" t="n"/>
+      <c r="K154" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L154" s="11" t="inlineStr">
+        <is>
+          <t>Testing epic (founder ask 2026-08-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>T10-13.12</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>BROWSER preview</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>Frontend/UX</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>Accessibility basics (in-browser)</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="inlineStr">
+        <is>
+          <t>Keyboard nav reaches + activates every control, visible focus rings, aria labels on icon buttons + dynamic content, colour contrast. The Epic 6 S16 a11y P0s, verified in-browser not just asserted.</t>
+        </is>
+      </c>
+      <c r="G155" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H155" s="11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I155" s="11" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J155" s="11" t="n"/>
+      <c r="K155" s="12" t="inlineStr">
+        <is>
+          <t>Grounded in code map 2026-08-29</t>
+        </is>
+      </c>
+      <c r="L155" s="11" t="inlineStr">
         <is>
           <t>Testing epic (founder ask 2026-08-29)</t>
         </is>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1077,6 +1077,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1126,19 +1127,19 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -1192,19 +1193,19 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -1324,19 +1325,19 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -1674,13 +1675,13 @@
       </c>
       <c r="I2" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J2" s="11" t="n"/>
       <c r="K2" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L2" s="11" t="inlineStr">
@@ -1730,13 +1731,13 @@
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J3" s="11" t="n"/>
       <c r="K3" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>In progress: execution+sales sub-scores unit-tested; finance+responsiveness need the DB company-view assembly (S1 continuation).</t>
         </is>
       </c>
       <c r="L3" s="11" t="inlineStr">
@@ -1842,13 +1843,13 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J5" s="11" t="n"/>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
@@ -1898,13 +1899,13 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J6" s="11" t="n"/>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
@@ -1954,13 +1955,13 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J7" s="11" t="n"/>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
@@ -2290,13 +2291,13 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J13" s="11" t="n"/>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
@@ -3130,13 +3131,13 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J28" s="11" t="n"/>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
@@ -3186,13 +3187,13 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J29" s="11" t="n"/>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
@@ -3242,13 +3243,13 @@
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J30" s="11" t="n"/>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
@@ -3298,13 +3299,13 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J31" s="11" t="n"/>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
@@ -6042,13 +6043,13 @@
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J80" s="11" t="n"/>
       <c r="K80" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L80" s="11" t="inlineStr">
@@ -6154,13 +6155,13 @@
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J82" s="11" t="n"/>
       <c r="K82" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L82" s="11" t="inlineStr">
@@ -6210,13 +6211,13 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J83" s="11" t="n"/>
       <c r="K83" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L83" s="11" t="inlineStr">
@@ -6266,13 +6267,13 @@
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J84" s="11" t="n"/>
       <c r="K84" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L84" s="11" t="inlineStr">
@@ -6322,13 +6323,13 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J85" s="11" t="n"/>
       <c r="K85" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_operating_score_unit.py + test_s1_finance_math_unit.py + test_s1_permissions_matrix_unit.py (70 unit tests, offline, green).</t>
         </is>
       </c>
       <c r="L85" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1127,14 +1127,14 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -1325,14 +1325,14 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -1731,13 +1731,13 @@
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J3" s="11" t="n"/>
       <c r="K3" s="12" t="inlineStr">
         <is>
-          <t>In progress: execution+sales sub-scores unit-tested; finance+responsiveness need the DB company-view assembly (S1 continuation).</t>
+          <t>Done 2026-08-29: tests/test_s1_captures_confidence_unit.py + test_s1_plans_quotas_unit.py + test_s1_operating_score_view_unit.py + payment-dup in test_s1_finance_math_unit.py (119 S1 unit tests total, green).</t>
         </is>
       </c>
       <c r="L3" s="11" t="inlineStr">
@@ -2011,13 +2011,13 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J8" s="11" t="n"/>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_captures_confidence_unit.py + test_s1_plans_quotas_unit.py + test_s1_operating_score_view_unit.py + payment-dup in test_s1_finance_math_unit.py (119 S1 unit tests total, green).</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
@@ -2067,13 +2067,13 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J9" s="11" t="n"/>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_captures_confidence_unit.py + test_s1_plans_quotas_unit.py + test_s1_operating_score_view_unit.py + payment-dup in test_s1_finance_math_unit.py (119 S1 unit tests total, green).</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
@@ -2123,13 +2123,13 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J10" s="11" t="n"/>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_captures_confidence_unit.py + test_s1_plans_quotas_unit.py + test_s1_operating_score_view_unit.py + payment-dup in test_s1_finance_math_unit.py (119 S1 unit tests total, green).</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
@@ -2179,13 +2179,13 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J11" s="11" t="n"/>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>In progress: effective_plan/seat/quota/feature resolution unit-tested; async check_quota over/fail-open needs a fake-DB (S10 continuation).</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
@@ -5931,13 +5931,13 @@
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J78" s="11" t="n"/>
       <c r="K78" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_captures_confidence_unit.py + test_s1_plans_quotas_unit.py + test_s1_operating_score_view_unit.py + payment-dup in test_s1_finance_math_unit.py (119 S1 unit tests total, green).</t>
         </is>
       </c>
       <c r="L78" s="11" t="inlineStr">
@@ -6547,13 +6547,13 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J89" s="11" t="n"/>
       <c r="K89" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_captures_confidence_unit.py + test_s1_plans_quotas_unit.py + test_s1_operating_score_view_unit.py + payment-dup in test_s1_finance_math_unit.py (119 S1 unit tests total, green).</t>
         </is>
       </c>
       <c r="L89" s="11" t="inlineStr">
@@ -6659,13 +6659,13 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J91" s="11" t="n"/>
       <c r="K91" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_captures_confidence_unit.py + test_s1_plans_quotas_unit.py + test_s1_operating_score_view_unit.py + payment-dup in test_s1_finance_math_unit.py (119 S1 unit tests total, green).</t>
         </is>
       </c>
       <c r="L91" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1325,14 +1325,14 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -2235,13 +2235,13 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J12" s="11" t="n"/>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>In progress: coerce_extract enum-clamp/confidence/summary covered (test_s1_extract_coercion_unit.py); Pydantic request-model sweep pending.</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
@@ -6379,13 +6379,13 @@
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J86" s="11" t="n"/>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s1_payment_matching_unit.py (number-match ambiguity, smart-match party+amount+30d window, allocation math) + fix pass.</t>
         </is>
       </c>
       <c r="L86" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -1787,13 +1787,13 @@
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J4" s="11" t="n"/>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: test_s1_models_validation_unit.py + test_s1_quota_check_unit.py + test_s1_operating_score_view_unit.py (Sprint 1 COMPLETE, 174 unit tests green).</t>
         </is>
       </c>
       <c r="L4" s="11" t="inlineStr">
@@ -2179,13 +2179,13 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J11" s="11" t="n"/>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>In progress: effective_plan/seat/quota/feature resolution unit-tested; async check_quota over/fail-open needs a fake-DB (S10 continuation).</t>
+          <t>Done 2026-08-29: test_s1_models_validation_unit.py + test_s1_quota_check_unit.py + test_s1_operating_score_view_unit.py (Sprint 1 COMPLETE, 174 unit tests green).</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
@@ -2235,13 +2235,13 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J12" s="11" t="n"/>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>In progress: coerce_extract enum-clamp/confidence/summary covered (test_s1_extract_coercion_unit.py); Pydantic request-model sweep pending.</t>
+          <t>Done 2026-08-29: test_s1_models_validation_unit.py + test_s1_quota_check_unit.py + test_s1_operating_score_view_unit.py (Sprint 1 COMPLETE, 174 unit tests green).</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1457,19 +1457,19 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -8507,13 +8507,13 @@
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J124" s="11" t="n"/>
       <c r="K124" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/conftest.py (with_test_db one-loop runner -&gt; fresh uniquely-named DB per test on the same Railway Mongo, dropped after; never founder-os-58) + tests/test_s11_db_isolation.py (6 tests, isolation + cleanup proven).</t>
         </is>
       </c>
       <c r="L124" s="11" t="inlineStr">
@@ -8619,13 +8619,13 @@
       </c>
       <c r="I126" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J126" s="11" t="n"/>
       <c r="K126" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/conftest.py (with_test_db one-loop runner -&gt; fresh uniquely-named DB per test on the same Railway Mongo, dropped after; never founder-os-58) + tests/test_s11_db_isolation.py (6 tests, isolation + cleanup proven).</t>
         </is>
       </c>
       <c r="L126" s="11" t="inlineStr">
@@ -8731,13 +8731,13 @@
       </c>
       <c r="I128" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J128" s="11" t="n"/>
       <c r="K128" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>In progress: unit/integration/db markers registered via conftest pytest_configure + new tests use them; bulk-tagging the existing 125 files pending.</t>
         </is>
       </c>
       <c r="L128" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1358,19 +1358,19 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -1457,14 +1457,14 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -6715,13 +6715,13 @@
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J92" s="11" t="n"/>
       <c r="K92" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s8_tenant_isolation.py on the isolated DB (10 tests): ensure_owned/owned_or_none/tenant_filter enforcement + cross-tenant read=404 &amp; write=0-modified across ALL 30 TENANT_COLLECTIONS; missing/cross indistinguishable.</t>
         </is>
       </c>
       <c r="L92" s="11" t="inlineStr">
@@ -6771,13 +6771,13 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J93" s="11" t="n"/>
       <c r="K93" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s8_tenant_isolation.py on the isolated DB (10 tests): ensure_owned/owned_or_none/tenant_filter enforcement + cross-tenant read=404 &amp; write=0-modified across ALL 30 TENANT_COLLECTIONS; missing/cross indistinguishable.</t>
         </is>
       </c>
       <c r="L93" s="11" t="inlineStr">
@@ -8787,13 +8787,13 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J129" s="11" t="n"/>
       <c r="K129" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s8_tenant_isolation.py on the isolated DB (10 tests): ensure_owned/owned_or_none/tenant_filter enforcement + cross-tenant read=404 &amp; write=0-modified across ALL 30 TENANT_COLLECTIONS; missing/cross indistinguishable.</t>
         </is>
       </c>
       <c r="L129" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1424,19 +1424,19 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -8003,13 +8003,13 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J115" s="11" t="n"/>
       <c r="K115" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done 2026-08-29: tests/test_s10_payment_concurrency.py on the isolated DB (3 tests) -- deterministically reproduces the missing-CAS double-allocation (two 1000 payments both fully allocate one 1000 invoice; sum applied 2000 vs invoice 1000) + the correct sequential contrast. BUG confirmed, fix pending.</t>
         </is>
       </c>
       <c r="L115" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1077,7 +1077,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -8009,7 +8008,7 @@
       <c r="J115" s="11" t="n"/>
       <c r="K115" s="12" t="inlineStr">
         <is>
-          <t>Done 2026-08-29: tests/test_s10_payment_concurrency.py on the isolated DB (3 tests) -- deterministically reproduces the missing-CAS double-allocation (two 1000 payments both fully allocate one 1000 invoice; sum applied 2000 vs invoice 1000) + the correct sequential contrast. BUG confirmed, fix pending.</t>
+          <t>Done + FIXED 2026-08-29: test reproduced the double-alloc; fixed _apply_payment_to_invoice with a compare-and-set on amount_paid + bounded re-read/retry (workflow-engine optimistic-concurrency pattern). Test flipped to assert correct behavior (one payment matches, the other stays unmatched). tests/test_s10_payment_concurrency.py.</t>
         </is>
       </c>
       <c r="L115" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +72,28 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00374151"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +125,11 @@
         <fgColor rgb="00F3F4F6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,6 +190,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10260,4 +10293,755 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Epic 10 -- Bug Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Defects surfaced by the testing effort (Sprint 1 unit + Sprint 8/10/11 DB tests). Every bug is pinned by a passing test; 'Fixed' rows link the fix commit, 'Flagged' rows are product decisions left to the founder, 'Disproven' rows were checked and are not bugs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>Tally: 10 findings -&gt; 3 Fixed, 6 Flagged (product decisions), 1 Disproven. Plus 4 test-infra/wiring items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Fix commit</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>Pinned by (test)</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>BUG-01</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Operating score</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Company-view did float(invoice.amount) with NO guard -&gt; a non-numeric OR OCR-formatted amount ('N/A', 'Rs 5,000') raised ValueError and crashed the ENTIRE operating score for the tenant.</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>e8d9b3c</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>test_s1_operating_score_view_unit.py</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>T10-07.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>BUG-02</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Finance / dedup</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate detection compared amounts with exact float == , so float-rounding (0.1+0.2 vs 0.3) escaped the amount-window rule.</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>e8d9b3c</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>test_s1_finance_math_unit.py</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>T10-07.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>BUG-03</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Finance / payments</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>_apply_payment_to_invoice was read-modify-write with NO CAS: two payments reconciling one invoice from a stale snapshot both allocated the full balance (double-allocation / lost update).</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>ed49c23</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>test_s10_payment_concurrency.py</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>T10-10.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>BUG-04</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Finance / parse</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>parse_amount accepts negative money ('-500' -&gt; -500.0), which flows unclamped into outstanding / net_profit.</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Flagged (product decision: credit notes / adjustments may be legitimate)</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>test_s1_finance_math_unit.py</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>T10-07.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>BUG-05</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Finance / ledger</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>_remaining goes negative on overpayment (no floor); negative remaining feeds contact/revenue outstanding sums.</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Flagged (product decision: negative = real overpayment credit; flooring would hide it)</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>test_s1_finance_math_unit.py</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>T10-07.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>BUG-06</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Operating score</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>An unassigned role-only task is credited to EVERY member of that role in _score_employees -&gt; N-way double-count of 'done'.</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Flagged (product decision: is a shared role task everyone's or no one's?)</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>test_s1_operating_score_unit.py</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>T10-07.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>BUG-07</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>RBAC / permissions</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>The 'operations' role is canonical + in DEFAULT_ROLES but has NO ROLE_DEFAULT_PERMS entry -&gt; silently falls back to base perms (no people/finance/ledger).</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Flagged (product decision: what should ops see by default?)</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>test_s1_permissions_matrix_unit.py</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>T10-03.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>BUG-08</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Operating score</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Company overall flips None&lt;-&gt;a number at exactly actionable 2-&gt;3 / inv_count 0-&gt;1 (new-tenant discontinuity); employee default 0 vs company 0.7 asymmetry.</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Flagged (product decision: unscored vs 70% for a data-thin tenant)</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>test_s1_operating_score_view_unit.py</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>T10-07.1 / T10-07.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>BUG-09</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Finance / dedup</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>_dup_reason: an unparseable date makes a same-amount same-vendor bill a duplicate regardless of how far apart.</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Flagged (defensible: conservative flagging routes to human review)</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>test_s1_finance_math_unit.py</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>T10-07.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>BUG-10</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Operating score vs finance_signals</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Initial code-map flagged a blank-due_date 'overdue' inconsistency between operating_score and finance_signals.</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Disproven by test: finance_signals._overdue_receivables ALSO guards blank dates (`if due and ...`) -&gt; both agree, no bug.</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>test_s1_operating_score_unit.py</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>T10-07.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>INF-01</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Test infra</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>test_tenant_deletion</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>KNOWN_TENANT_SCOPED_COLLECTIONS never picked up the brain_contexts-&gt;brain_query_cache rename -&gt; drift test red against the authoritative delete list.</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>89dd758</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>test_tenant_deletion.py</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>INF-02</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Test infra</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>test_operating_score_role_split</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Stale source-grep test read server.py for functions the Epic 8 refactor moved to routers/services operating_score.py.</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>Fixed (repointed)</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>e8d9b3c</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>test_operating_score_role_split.py</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>INF-03</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Wiring</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>S9 compliance</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>The S9 commit captured stale copies of 4 modified files (routing/schedulers/AdminPortal/baseline) -- compliance router was unregistered on HEAD.</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>Fixed (recovered)</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>2929b47</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>test_api_parity.py</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>INF-04</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Test infra</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>test_brain_write_coverage</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>TestNewWriteSites greps server.py for the workflow-advance brain_context write (moved by the refactor) -&gt; 2 stale failures.</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Open (pre-existing, unrelated to fixes above)</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>test_brain_write_coverage.py</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -157,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,6 +198,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1110,6 +1111,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -8595,13 +8597,13 @@
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J125" s="11" t="n"/>
       <c r="K125" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>In progress: stale-test cleanup fixed 39 pre-existing failures across 9 source-grep suites (repointed to Epic-8 homes). Remaining: the iteration_* live suite (needs the isolated-DB backend) + test_workflows_dynamic event-loop harness (INF-06).</t>
         </is>
       </c>
       <c r="L125" s="11" t="inlineStr">
@@ -8931,13 +8933,13 @@
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J131" s="11" t="n"/>
       <c r="K131" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>In progress: triaged the 27 source-grep suites -&gt; 9 fixed. Remaining tail categorized in Bug Log INF-06 (event-loop harness) + INF-07 (mixed shim + possibly-real behavioural fake-DB failures).</t>
         </is>
       </c>
       <c r="L131" s="11" t="inlineStr">
@@ -10301,7 +10303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11020,24 +11022,165 @@
           <t>TestNewWriteSites greps server.py for the workflow-advance brain_context write (moved by the refactor) -&gt; 2 stale failures.</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>Open (pre-existing, unrelated to fixes above)</t>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>Fixed (repointed to services.workflow_engine.advance)</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
+          <t>5ef38b4</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>test_brain_write_coverage.py</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>test_brain_write_coverage.py</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>INF-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Test infra</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>stale-test cleanup (9 files)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Source-inspection tests grepped server.py for functions/routes/index code the Epic 8 refactor moved to routers/services/bootstrap. Repointed imports + getsource targets + a compat shim + the WE-07 writer allowlist.</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>Fixed (39 stale failures -&gt; green across 9 files)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>e518077/1d2d854/065732e/5ef38b4</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>test_audit_log, test_plans_and_ai_keys, test_rbac_wave3_role_model, test_session_revocation, test_we07, test_we_stage_version_init, test_brain_hygiene, test_brain_write_coverage, test_rbac_wave3_gates</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>T10-11.2 / T10-11.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>INF-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Test infra</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>test_workflows_dynamic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>All 11 failures are 'Cannot use AsyncMongoClient in different event loop' -- the test reuses one async client across asyncio.run calls (Motor tolerated this; PyMongo AsyncMongoClient binds to one loop). A harness bug from the Motor-&gt;PyMongo-async migration, not stale-source and not a code bug.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Open -- needs async-harness rewrite (one-loop pattern, like conftest.with_test_db)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>test_workflows_dynamic.py</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>T10-11.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>INF-07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Needs investigation</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>test_tenant_phone_routing + test_tenancy_hygiene_batch</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Remaining tail (8): a few more moved-fn shims/repoints (resolve_wa_tenant, whatsapp_logs, tenant_terminal_stages) PLUS behavioural fake-DB failures (resolve_wa_tenant returns a UUID not the expected tenant; tenant-scoped task lookup returns 0) that may be REAL regressions -- flagged for investigation, not blind-shimmed.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Open -- triage: separate the source-grep repoints from possibly-real behaviour</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>test_tenant_phone_routing.py, test_tenancy_hygiene_batch.py</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>T10-11.8</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1111,7 +1111,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -8939,7 +8938,7 @@
       <c r="J131" s="11" t="n"/>
       <c r="K131" s="12" t="inlineStr">
         <is>
-          <t>In progress: triaged the 27 source-grep suites -&gt; 9 fixed. Remaining tail categorized in Bug Log INF-06 (event-loop harness) + INF-07 (mixed shim + possibly-real behavioural fake-DB failures).</t>
+          <t>In progress: triaged the 27 source-grep suites -&gt; 9 fixed. Remaining tail categorized in Bug Log INF-06 (event-loop harness) + INF-07 (mixed shim + possibly-real behavioural fake-DB failures). | 2026-08-29: event-loop flakiness eliminated -- 14 files converted off get_event_loop()/stale-patch to dedicated per-module loops; +118 tests deterministic. Remaining non-determinism is env-gated (REACT_APP_BACKEND_URL / live server) = T10-11.2.</t>
         </is>
       </c>
       <c r="L131" s="11" t="inlineStr">
@@ -11113,12 +11112,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>All 11 failures are 'Cannot use AsyncMongoClient in different event loop' -- the test reuses one async client across asyncio.run calls (Motor tolerated this; PyMongo AsyncMongoClient binds to one loop). A harness bug from the Motor-&gt;PyMongo-async migration, not stale-source and not a code bug.</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Open -- needs async-harness rewrite (one-loop pattern, like conftest.with_test_db)</t>
+          <t>test_workflows_dynamic monkeypatched server.tenant_operating_model, but Epic 8 moved that resolver to services.ai.generators (resolved at call-time via `from ... import`), so the patch was DEAD: the real DB-backed resolver ran, bound the module-level AsyncMongoClient to the first asyncio.run() loop, and every later test crashed 'Cannot use AsyncMongoClient in different event loop'. So the summary's 'event-loop harness' label was only a symptom -- real cause = stale monkeypatch. Separately, 13 unit files used `asyncio.get_event_loop().run_until_complete`, which under -n/--dist loadscope reuses a SIBLING module's already-closed loop -&gt; 'Event loop is closed'.</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>Fixed -- (a) repointed the stale patch to services.ai.generators (test_workflows_dynamic 20-&gt;31 green, and now tests real tenant-specific pipelines instead of passing by accident via the textile default); (b) converted 13 files' _run helper from get_event_loop() to a dedicated module-scoped loop (_LOOP = asyncio.new_event_loop()). Result: full non-iteration suite 1075-&gt;1193 passing (+118), zero event-loop errors remain under -n2 --dist loadscope.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -11128,7 +11127,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>test_workflows_dynamic.py</t>
+          <t>test_workflows_dynamic.py + 13 _run-helper files (audit_log, quotas, rbac_wave1, session_mgmt, ...)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -11160,12 +11159,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Remaining tail (8): a few more moved-fn shims/repoints (resolve_wa_tenant, whatsapp_logs, tenant_terminal_stages) PLUS behavioural fake-DB failures (resolve_wa_tenant returns a UUID not the expected tenant; tenant-scoped task lookup returns 0) that may be REAL regressions -- flagged for investigation, not blind-shimmed.</t>
+          <t>After the INF-06 fix, the phone/tenancy tail fails IDENTICALLY in isolation, so it is not event-loop related: test_tenant_phone_routing = 1 stale source-grep (asserts server.whatsapp_logs, which Epic 8 moved off server.py) + 4 behavioral resolve_wa_tenant assertions (multi-tenant WA collision routing); test_tenancy_hygiene_batch = enrich-decisions tenant-guard + dynamic-terminals assertions. These are real-code behavioral checks to investigate, distinct from the harness fix.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Open -- triage: separate the source-grep repoints from possibly-real behaviour</t>
+          <t>Open -- behavioral/stale-source tail (NOT loop). Next: repoint the whatsapp_logs grep, then investigate the resolve_wa_tenant multi-tenant assertions for a possible real routing regression.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -10302,7 +10302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11159,12 +11159,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>After the INF-06 fix, the phone/tenancy tail fails IDENTICALLY in isolation, so it is not event-loop related: test_tenant_phone_routing = 1 stale source-grep (asserts server.whatsapp_logs, which Epic 8 moved off server.py) + 4 behavioral resolve_wa_tenant assertions (multi-tenant WA collision routing); test_tenancy_hygiene_batch = enrich-decisions tenant-guard + dynamic-terminals assertions. These are real-code behavioral checks to investigate, distinct from the harness fix.</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Open -- behavioral/stale-source tail (NOT loop). Next: repoint the whatsapp_logs grep, then investigate the resolve_wa_tenant multi-tenant assertions for a possible real routing regression.</t>
+          <t>test_tenant_phone_routing (5): resolve_wa_tenant + whatsapp_logs moved off server.py in Epic 8 (-&gt; services/whatsapp.py, routers/whatsapp.py) where they resolve db/push_notification/_owner_ids as THAT module's globals. The test still monkeypatched server.db / server.push_notification / server._owner_ids -- all dead -- so resolve_wa_tenant ran against the REAL hosted DB (returned a live UUID tenant instead of the fake 't1') and could have fired real update_many/push_notification side effects. NOT a product bug: with the fake DB correctly installed, every multi-tenant safety assertion passes (no obsolete-marking on cross-tenant collision, both owners notified, WA_TENANT_ID fallback, within-tenant tenant_id guard) -- the function is correct.</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>Fixed -- repointed the monkeypatch to services.whatsapp (db/push_notification/_owner_ids) and the whatsapp_logs source-grep to routers.whatsapp. test_tenant_phone_routing 17-&gt;22 green; also closes a hazard (stale test reading/mutating shared founder-os-58 -&gt; reinforces T10-11.1 isolated DB).</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -11174,12 +11174,59 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>test_tenant_phone_routing.py, test_tenancy_hygiene_batch.py</t>
+          <t>test_tenant_phone_routing.py (TestResolveWaTenantMultiTenant + TestWhatsappLogsTenantIsolation)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>T10-11.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>INF-08</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Test infra</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>test_tenancy_hygiene_batch</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Remaining INF-07 tail after the phone-routing fix: 5 failures in TestEnrichDecisionsTenantGuard (enrich-decisions tenant-scoping of task/creator lookups) + TestActiveWorkflowsUsesDynamicTerminals. Fail identically in isolation -&gt; not loop/env; a mix of source-grep repoints and behavioral tenant-guard assertions to investigate.</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Open -- next INF-07-class item (separate from resolve_wa_tenant, which is fixed).</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>test_tenancy_hygiene_batch.py</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -11206,12 +11206,12 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Remaining INF-07 tail after the phone-routing fix: 5 failures in TestEnrichDecisionsTenantGuard (enrich-decisions tenant-scoping of task/creator lookups) + TestActiveWorkflowsUsesDynamicTerminals. Fail identically in isolation -&gt; not loop/env; a mix of source-grep repoints and behavioral tenant-guard assertions to investigate.</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>Open -- next INF-07-class item (separate from resolve_wa_tenant, which is fixed).</t>
+          <t>test_tenancy_hygiene_batch (3 in isolation / 5 under -n): (a) enrich_decision/enrich_decisions moved to services/enrich.py, which resolve db (&lt;-core) and enrich_tasks (&lt;-services.tasks) as THAT module's globals; the test patched server.db / server.enrich_tasks (dead) so the id-lookups ran against the REAL hosted DB (the 2 assertions needing fake rows failed; the other 2 passed vacuously vs the empty real DB). (b) the active_workflows counter moved to routers/dashboard.py, so the source-grep on server.py could no longer see `await tenant_terminal_stages(tid)`. NOT a product bug: enrich_decision correctly scopes BOTH task_ids and created_by by tenant_id (and skips inference on a mixed batch); the dashboard counter correctly awaits tenant_terminal_stages.</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>Fixed -- _install patches services.enrich (db/enrich_tasks); counter source-grep reads routers.dashboard. test_tenancy_hygiene_batch 7-&gt;10 green (full non-iteration suite 1202-&gt;1204). Anti-pattern sweep: no other test file still does setattr(server,'db') -- phone_routing + tenancy_hygiene were the only two real-DB-leak instances, both closed.</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>test_tenancy_hygiene_batch.py</t>
+          <t>test_tenancy_hygiene_batch.py (TestEnrichDecisionsTenantGuard + TestActiveWorkflowsUsesDynamicTerminals)</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -8594,7 +8594,7 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I125" s="11" t="inlineStr">
+      <c r="I125" s="13" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
@@ -8602,7 +8602,7 @@
       <c r="J125" s="11" t="n"/>
       <c r="K125" s="12" t="inlineStr">
         <is>
-          <t>In progress: stale-test cleanup fixed 39 pre-existing failures across 9 source-grep suites (repointed to Epic-8 homes). Remaining: the iteration_* live suite (needs the isolated-DB backend) + test_workflows_dynamic event-loop harness (INF-06).</t>
+          <t>SCOPED + Phase-1 spike DONE (2026-08-29). Landscape: 55/141 test files are live-integration (HTTP via requests); 45 default to the HOSTED preview URL (safety risk: silent writes to a shared remote env), 12 hard-require the env (the collection errors). App DB = MONGO_URL+DB_NAME env; bootstrap self-seeds admin@decisionos.biz + the Sharma demo (owner@sharma.com) = exactly the identities the tests log in as. HARNESS BUILT: tests/_live_harness.py boots uvicorn on an ISOLATED db (dos_test_live_*, never founder-os-58), pins creds/AUTH_RETURN_TOKEN/COOKIE_SECURE, waits for seed via DIRECT DB-poll (NOT login-poll -- that trips the brute-force rate limiter), runs, then drops the db. Proof: test_iteration60_admin.py 16/16 green end-to-end. PHASES: P1 harness [DONE] -&gt; P2 kill the 45 hosted-preview URL defaults (fail-closed base_url helper) -&gt; P3 determinism (seed-vs-clean assumptions, cross-file writes under -n, the /app/memory WinError, per-file stale assertions like the ai-keys set) -&gt; P4 @integration/@unit markers + CI gate (feeds T10-11.5/11.4) -&gt; P5 (optional) in-process ASGI for the hottest files.</t>
         </is>
       </c>
       <c r="L125" s="11" t="inlineStr">
@@ -10302,7 +10302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11230,6 +11230,53 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>INF-09</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Test infra / dev-ergonomics</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>core/security.py auth cookies</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Auth + CSRF + admin cookies were set with secure=True HARDCODED, so cookie-authed endpoints (admin console, cookie-session flows) 401 under the local http integration harness -- `requests` won't send a Secure cookie over http://127.0.0.1. On the hosted https preview they work, which is why the tests were green there. Blocks running the cookie-authed slice of the 55-file integration suite locally/CI.</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>Fixed -- added COOKIE_SECURE config (defaults True EVERYWHERE incl. every https deploy; ONLY an explicit COOKIE_SECURE=0 relaxes it, which the harness sets). Offline suite unchanged (1204 pass), cookie/csrf/auth-hardening 56/56 green.</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>config.py + core/security.py</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>tests/_live_harness.py (harness)</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>T10-11.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -8602,7 +8602,7 @@
       <c r="J125" s="11" t="n"/>
       <c r="K125" s="12" t="inlineStr">
         <is>
-          <t>SCOPED + Phase-1 spike DONE (2026-08-29). Landscape: 55/141 test files are live-integration (HTTP via requests); 45 default to the HOSTED preview URL (safety risk: silent writes to a shared remote env), 12 hard-require the env (the collection errors). App DB = MONGO_URL+DB_NAME env; bootstrap self-seeds admin@decisionos.biz + the Sharma demo (owner@sharma.com) = exactly the identities the tests log in as. HARNESS BUILT: tests/_live_harness.py boots uvicorn on an ISOLATED db (dos_test_live_*, never founder-os-58), pins creds/AUTH_RETURN_TOKEN/COOKIE_SECURE, waits for seed via DIRECT DB-poll (NOT login-poll -- that trips the brute-force rate limiter), runs, then drops the db. Proof: test_iteration60_admin.py 16/16 green end-to-end. PHASES: P1 harness [DONE] -&gt; P2 kill the 45 hosted-preview URL defaults (fail-closed base_url helper) -&gt; P3 determinism (seed-vs-clean assumptions, cross-file writes under -n, the /app/memory WinError, per-file stale assertions like the ai-keys set) -&gt; P4 @integration/@unit markers + CI gate (feeds T10-11.5/11.4) -&gt; P5 (optional) in-process ASGI for the hottest files.</t>
+          <t>SCOPED + Phase-1 spike DONE (2026-08-29). Landscape: 55/141 test files are live-integration (HTTP via requests); 45 default to the HOSTED preview URL (safety risk: silent writes to a shared remote env), 12 hard-require the env (the collection errors). App DB = MONGO_URL+DB_NAME env; bootstrap self-seeds admin@decisionos.biz + the Sharma demo (owner@sharma.com) = exactly the identities the tests log in as. HARNESS BUILT: tests/_live_harness.py boots uvicorn on an ISOLATED db (dos_test_live_*, never founder-os-58), pins creds/AUTH_RETURN_TOKEN/COOKIE_SECURE, waits for seed via DIRECT DB-poll (NOT login-poll -- that trips the brute-force rate limiter), runs, then drops the db. Proof: test_iteration60_admin.py 16/16 green end-to-end. PHASES: P1 harness [DONE] -&gt; P2 kill the 45 hosted-preview URL defaults (fail-closed base_url helper) -&gt; P3 determinism (seed-vs-clean assumptions, cross-file writes under -n, the /app/memory WinError, per-file stale assertions like the ai-keys set) -&gt; P4 @integration/@unit markers + CI gate (feeds T10-11.5/11.4) -&gt; P5 (optional) in-process ASGI for the hottest files. || P2 DONE (2026-08-29): added tests/integration_base.base_url() -- one env-only, fail-closed source; repointed all 55 HTTP integration files off their hosted-preview / frontend-.env defaults. Unset env now SKIPS the module (55 skipped) instead of erroring or silently hitting a shared remote. Also repointed 2 stale `motor` imports -&gt; pymongo. Canonical xdist suite: 1207 passed / 15 failed / 0 errors (was 88 BACKEND_URL errors); the 15 are the pre-existing offline-behavioral tail (ai_consent, onboarding_flow, epic3_*, quotas) unrelated to P2. Next: P3 determinism/assertions, P4 markers+CI.</t>
         </is>
       </c>
       <c r="L125" s="11" t="inlineStr">
@@ -10302,7 +10302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11277,6 +11277,53 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>INF-10</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Safety / test infra</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>55 live-integration files</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>45 of the 55 HTTP integration files DEFAULTED to a hardcoded hosted-preview URL (founder-os-58.preview.emergentagent.com), and the _load_frontend_env helpers read frontend/.env (a deployed backend) -- so a run with REACT_APP_BACKEND_URL unset fired real register/create/delete calls at a shared remote environment. 12 others hard-crashed (KeyError) and 2 failed to even import (stale `motor` dependency, removed in Epic 8).</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>Fixed -- new tests/integration_base.base_url() is the single env-only, fail-closed source (unset -&gt; module-level skip, never a remote default, never reads frontend/.env). All 55 files repointed; 2 motor imports -&gt; pymongo AsyncMongoClient. Unset env now yields 55 clean skips, 0 remote-hit risk.</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>config n/a</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>tests/integration_base.py + 55 files</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>T10-11.2 P2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -10302,7 +10302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11324,6 +11324,53 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>INF-11</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Test infra</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>15 offline failures + 8 flaky exposed</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Cleared the offline-behavioral tail: ai_consent/epic2/quotas = stale `from server import X` (Epic 8 moved them to routers.tenant_settings/finance); onboarding_flow = dead monkeypatch on server.ai_generate_* (wrappers resolve from services.ai.generators, so the REAL AI fns ran -- 2 assertions failed, 3 passed while making live AI calls); epic3 s5/s9/s10 = live-DB tests using `from database import db` + asyncio.run that mutated founder-os-58 AND cross-loop-flaked. Clearing these reshuffled -n/loadscope and exposed 8 shim-fragility failures (source-grep tests depending on a module-level setattr(server, X) shim that a monkeypatch in another module deletes on teardown).</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>Fixed -- repointed stale imports to real modules; retargeted onboarding_flow patches to services.ai.generators (also stops real AI calls); migrated epic3 s5/s9/s10 to with_test_db + patched the service module's db (isolated DB, one loop, no founder-os-58); repointed the 4 shim files' source-grep tests from server.X to the robust module-level _shim_X import. Full xdist suite now 1222 passed / 0 failed / 0 errors, stable across repeated runs.</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>n/a (test-only)</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>11 test files</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>offline tail</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -157,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -199,6 +199,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8602,7 +8605,7 @@
       <c r="J125" s="11" t="n"/>
       <c r="K125" s="12" t="inlineStr">
         <is>
-          <t>SCOPED + Phase-1 spike DONE (2026-08-29). Landscape: 55/141 test files are live-integration (HTTP via requests); 45 default to the HOSTED preview URL (safety risk: silent writes to a shared remote env), 12 hard-require the env (the collection errors). App DB = MONGO_URL+DB_NAME env; bootstrap self-seeds admin@decisionos.biz + the Sharma demo (owner@sharma.com) = exactly the identities the tests log in as. HARNESS BUILT: tests/_live_harness.py boots uvicorn on an ISOLATED db (dos_test_live_*, never founder-os-58), pins creds/AUTH_RETURN_TOKEN/COOKIE_SECURE, waits for seed via DIRECT DB-poll (NOT login-poll -- that trips the brute-force rate limiter), runs, then drops the db. Proof: test_iteration60_admin.py 16/16 green end-to-end. PHASES: P1 harness [DONE] -&gt; P2 kill the 45 hosted-preview URL defaults (fail-closed base_url helper) -&gt; P3 determinism (seed-vs-clean assumptions, cross-file writes under -n, the /app/memory WinError, per-file stale assertions like the ai-keys set) -&gt; P4 @integration/@unit markers + CI gate (feeds T10-11.5/11.4) -&gt; P5 (optional) in-process ASGI for the hottest files. || P2 DONE (2026-08-29): added tests/integration_base.base_url() -- one env-only, fail-closed source; repointed all 55 HTTP integration files off their hosted-preview / frontend-.env defaults. Unset env now SKIPS the module (55 skipped) instead of erroring or silently hitting a shared remote. Also repointed 2 stale `motor` imports -&gt; pymongo. Canonical xdist suite: 1207 passed / 15 failed / 0 errors (was 88 BACKEND_URL errors); the 15 are the pre-existing offline-behavioral tail (ai_consent, onboarding_flow, epic3_*, quotas) unrelated to P2. Next: P3 determinism/assertions, P4 markers+CI.</t>
+          <t>SCOPED + Phase-1 spike DONE (2026-08-29). Landscape: 55/141 test files are live-integration (HTTP via requests); 45 default to the HOSTED preview URL (safety risk: silent writes to a shared remote env), 12 hard-require the env (the collection errors). App DB = MONGO_URL+DB_NAME env; bootstrap self-seeds admin@decisionos.biz + the Sharma demo (owner@sharma.com) = exactly the identities the tests log in as. HARNESS BUILT: tests/_live_harness.py boots uvicorn on an ISOLATED db (dos_test_live_*, never founder-os-58), pins creds/AUTH_RETURN_TOKEN/COOKIE_SECURE, waits for seed via DIRECT DB-poll (NOT login-poll -- that trips the brute-force rate limiter), runs, then drops the db. Proof: test_iteration60_admin.py 16/16 green end-to-end. PHASES: P1 harness [DONE] -&gt; P2 kill the 45 hosted-preview URL defaults (fail-closed base_url helper) -&gt; P3 determinism (seed-vs-clean assumptions, cross-file writes under -n, the /app/memory WinError, per-file stale assertions like the ai-keys set) -&gt; P4 @integration/@unit markers + CI gate (feeds T10-11.5/11.4) -&gt; P5 (optional) in-process ASGI for the hottest files. || P2 DONE (2026-08-29): added tests/integration_base.base_url() -- one env-only, fail-closed source; repointed all 55 HTTP integration files off their hosted-preview / frontend-.env defaults. Unset env now SKIPS the module (55 skipped) instead of erroring or silently hitting a shared remote. Also repointed 2 stale `motor` imports -&gt; pymongo. Canonical xdist suite: 1207 passed / 15 failed / 0 errors (was 88 BACKEND_URL errors); the 15 are the pre-existing offline-behavioral tail (ai_consent, onboarding_flow, epic3_*, quotas) unrelated to P2. Next: P3 determinism/assertions, P4 markers+CI. || P4 DONE (2026-08-29): convention-based tiering (conftest) + .github/workflows/tests.yml (unit gate blocking; db + integration best-effort) + backend/tests/README.md. Full suite 1222 pass, unit gate 1200 pass offline.</t>
         </is>
       </c>
       <c r="L125" s="11" t="inlineStr">
@@ -8706,15 +8709,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I127" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I127" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J127" s="11" t="n"/>
       <c r="K127" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>P4 (2026-08-29): .github/workflows/tests.yml -- unit job is the BLOCKING offline gate (1200 passed in ~32s, dummy env, provider keys blanked); db job runs -m db (skips cleanly without MONGO_URL secret); integration job boots the isolated-DB harness (non-blocking until P3). Installs emergentintegrations from its CDN + dummy EMERGENT_LLM_KEY. Docs: backend/tests/README.md.</t>
         </is>
       </c>
       <c r="L127" s="11" t="inlineStr">
@@ -8762,15 +8765,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I128" s="11" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="I128" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J128" s="11" t="n"/>
       <c r="K128" s="12" t="inlineStr">
         <is>
-          <t>In progress: unit/integration/db markers registered via conftest pytest_configure + new tests use them; bulk-tagging the existing 125 files pending.</t>
+          <t>P4 (2026-08-29): auto-tiered by convention in conftest.pytest_collection_modifyitems -- unit (~1200, offline) / integration (~850, base_url) / db (~22, with_test_db). No per-file tagging. Verified counts + `pytest -m unit` green offline with dummy keys.</t>
         </is>
       </c>
       <c r="L128" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -6021,15 +6021,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I79" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I79" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J79" s="11" t="n"/>
       <c r="K79" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s7_finance_formula.test_blank_due_date_not_overdue_in_either_engine: both operating_score and finance_signals._overdue_receivables guard blank due_date (`if due and ...`) -&gt; consistent, blank is never overdue (confirms BUG-10 disproven).</t>
         </is>
       </c>
       <c r="L79" s="11" t="inlineStr">
@@ -6133,15 +6133,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I81" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J81" s="11" t="n"/>
       <c r="K81" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- BUG FOUND + FIXED. operating_score summed db.payments with NO direction filter, so outbound supplier payments (direction='out') inflated 'collected'/outstanding. Added direction:'in'. Pinned by test_s7_finance_formula.test_operating_score_collected_excludes_out_payments. See BUG-11.</t>
         </is>
       </c>
       <c r="L81" s="11" t="inlineStr">
@@ -6469,15 +6469,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I87" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I87" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J87" s="11" t="n"/>
       <c r="K87" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s7_finance_formula.test_invoice_settle_epsilon_0_01: money is 2-decimal rounded, so settle bites at whole-paise -- 0.01 short still settles (paid), 0.02 stays partial.</t>
         </is>
       </c>
       <c r="L87" s="11" t="inlineStr">
@@ -6525,15 +6525,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I88" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I88" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J88" s="11" t="n"/>
       <c r="K88" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s7_finance_formula.test_followup_escalation_ladder_and_idempotency: days&lt;1-&gt;L1, &lt;2-&gt;L2, &lt;3-&gt;L3, else-&gt;L4; second run re-escalates nothing (target&lt;=escalation_level guard).</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr">
@@ -6637,15 +6637,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I90" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I90" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J90" s="11" t="n"/>
       <c r="K90" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s7_finance_formula.test_net_profit_billed_not_cash_and_mixed_currency_no_fx: net_profit = revenue BILLED - ALL expenses (accrual, not cash); mixed INR+USD summed raw, no FX.</t>
         </is>
       </c>
       <c r="L90" s="11" t="inlineStr">
@@ -10305,7 +10305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11374,6 +11374,53 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>BUG-11</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Operating score / finance</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>The finance sub-score summed db.payments with no direction filter, but that collection holds BOTH inbound customer payments (direction='in') and outbound supplier payments (direction='out'). So out-payments inflated total_paid -&gt; 'collected' ratio overstated and 'outstanding' understated (could go negative). A tenant paying suppliers looked like they had collected more from customers.</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>Fixed -- added direction:'in' to the operating_score payments query (services/operating_score.py).</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>test_s7_finance_formula.py</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>T10-07.4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -3389,15 +3389,15 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J32" s="11" t="n"/>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s3_role_matrix.test_every_write_endpoint_is_gated_or_explicitly_public: static contract over the live app -- 192 write routes, 168 gated (require_perm/role/ledger), 24 on the deliberate public allow-list (signup/login/onboarding/webhooks). ZERO accidentally-ungated writes; any new one fails the test.</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
@@ -3445,15 +3445,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J33" s="11" t="n"/>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s3_role_matrix: require_ledger denies sales/operations/custom (403), allows finance+owner; _can_finance predicate role-correct (+ explicit finance grant flips it on). Brain LLM-intent PERMISSION_DENIED path is integration (covered by _can_finance here).</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
@@ -3501,15 +3501,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I34" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J34" s="11" t="n"/>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s3_role_matrix: require_role('owner') denies EVERY non-owner role incl. custom, allows owner. The owner-only guarantee at the primitive.</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
@@ -3557,15 +3557,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J35" s="11" t="n"/>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s3_role_matrix: brain_export in PERMISSION_KEYS but not in _BASE_PERMS / any ROLE_DEFAULT_PERMS / non-owner user_perms; owner has it; ABSENT from frontend perms.js -&gt; owner-only-by-omission, ungrantable via UI.</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
@@ -3613,15 +3613,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I36" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J36" s="11" t="n"/>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s3_role_matrix.test_team_manage_does_not_satisfy_owner_gate: a non-owner holding team_manage still gets 403 from require_role('owner') -- backend owner gates are role-based, not perm-based.</t>
         </is>
       </c>
       <c r="L36" s="11" t="inlineStr">
@@ -3669,15 +3669,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I37" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J37" s="11" t="n"/>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s3_role_matrix.test_temp_grant_unions_then_expires: active temp_grant unions a perm on top of role perms; expired grant drops; unknown key ignored; never removes a base perm.</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -2549,15 +2549,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J17" s="11" t="n"/>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_contact_rename_cascade_and_outstanding_split: rename cascades contact_name into invoices+payments and counterparty on workflows (by contact_id); outstanding_by_contact splits purchase_bill-&gt;payables (400) vs sales-&gt;receivables (1000).</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
@@ -2997,15 +2997,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J25" s="11" t="n"/>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_inbox_counts_full_open_total_and_status_validation: list paginates (limit=2) but counts + open_total reflect the FULL open set (5, complaint=3/payment=2); bad status-&gt;400, missing id-&gt;404.</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
@@ -3109,15 +3109,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J27" s="11" t="n"/>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_operating_score_viewer_dispatch_and_privacy: owner-&gt;company view(+my_snapshot), non-owner-&gt;self, owner ?user_id-&gt;target self-view+view_as, non-owner ?user_id-&gt;403 (privacy), owner-&gt;ghost-&gt;404.</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -2493,15 +2493,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J16" s="11" t="n"/>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_workflow_create_and_advance_gating: create validates type (unknown-&gt;400), starts at stage[0]; advance with an open stage task-&gt;409; override without reason-&gt;400; audited override (with reason) forces the transition.</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
@@ -2885,15 +2885,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J23" s="11" t="n"/>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_complaint_log_resolve_and_memory: log (status open + auto-inbox), resolve writes a 'resolution' brain_context row, missing-&gt;404, memory write+read round-trips (write gated on brain).</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -2381,15 +2381,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J14" s="11" t="n"/>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_decision_approve_and_reject_lifecycle: approve -&gt; status approved, blocked tasks unblocked (todo), procurement workflow auto-advances requested-&gt;approved, writes a 'decision' brain_context row; reject -&gt; status rejected, cascade-deletes tasks/workflows/calendar (NO orphans), dismisses the inbox item; missing decision -&gt; 404.</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -2437,15 +2437,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J15" s="11" t="n"/>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_task_gates_smart_route_and_auto_invoice: role task with no assignee auto-routes to the least-loaded member; evidence_required blocks done without proof (400); unapproved task can't start (403); valid done -&gt; status done + progress 100; invalid status 400, missing 404; completing an invoice-task auto-creates a draft invoice, idempotent by source_task_id.</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -2941,15 +2941,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J24" s="11" t="n"/>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_leave_request_validation_approve_and_attendance: unknown leave type-&gt;400, end-before-start-&gt;400, valid request-&gt;pending, approve (leave_approve)-&gt;approved; attendance upserts one row per (user,date) with latest-mark-wins.</t>
         </is>
       </c>
       <c r="L24" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -3053,15 +3053,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J26" s="11" t="n"/>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_whatsapp_verify_and_webhook_gates: GET verify echoes challenge only on mode+token match (else 403); POST no WA_ACCESS_TOKEN-&gt;JSON no-op; configured+signature mismatch-&gt;403; prod without WA_APP_SECRET-&gt;503. (whatsapp_logs tenant-scoping pinned in test_tenant_phone_routing.)</t>
         </is>
       </c>
       <c r="L26" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -2605,15 +2605,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J18" s="11" t="n"/>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_ingest_commit_is_idempotent: commit files an ingestion (status-&gt;filed, closes source inbox item), committing an already-filed upload-&gt;400, missing-&gt;404. (AI OCR extract-fail-records-failed path is integration/mock-heavy.)</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
@@ -2661,15 +2661,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J19" s="11" t="n"/>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_ledger_typed_crud_payment_match_and_delete_cascade: typed expense CRUD; inbound partial payment leaves invoice partial; overpay settles invoice + leaves remainder on payment; no confident match-&gt;unmatched; delete revenue cascades its payments; missing-&gt;404.</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
@@ -2717,15 +2717,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J20" s="11" t="n"/>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_ask_finance_intent_denied_and_insufficient_data: money-disclosure guarded at TWO layers -- intent gate (non-finance user asking sales-&gt;PERMISSION_DENIED) and plan gate (needs_finance plan-&gt;PERMISSION_DENIED for non-finance). Export uses the separate brain_export perm (see T10-03.8).</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
@@ -2773,15 +2773,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J21" s="11" t="n"/>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional (voice): text note queues process_voice_note; empty directive+no attachment-&gt;400; transcribe_only surfaces an STT provider failure as 503.</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
@@ -2829,15 +2829,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J22" s="11" t="n"/>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s2_functional.test_meeting_text_intake_and_cross_tenant_404: /meetings/text creates a record in 'Processing meeting…' queued state; get_meeting is tenant-scoped (cross-tenant + missing-&gt;404).</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -6917,15 +6917,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I95" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I95" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J95" s="11" t="n"/>
       <c r="K95" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s8_isolation_scenarios.test_file_serve_by_name_tenant_scope_and_traversal: path traversal (../, leading-dot, slash) -&gt; 404; a file owned by another tenant is not resolvable in the caller's scope -&gt; 404.</t>
         </is>
       </c>
       <c r="L95" s="11" t="inlineStr">
@@ -6973,15 +6973,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I96" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I96" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J96" s="11" t="n"/>
       <c r="K96" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s8_isolation_scenarios.test_whatsapp_logs_hide_other_tenants_and_unrouted: owner of A sees ONLY A's wa_events -- never tenant B's, never unrouted (tenant_id=None) events.</t>
         </is>
       </c>
       <c r="L96" s="11" t="inlineStr">
@@ -7141,15 +7141,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I99" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I99" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J99" s="11" t="n"/>
       <c r="K99" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s8_isolation_scenarios.test_tenant_deletion_removes_A_and_keeps_B: seed A+B in EVERY TENANT_COLLECTIONS collection, delete A -&gt; 0 rows for A across all + tenant doc gone; B fully intact; missing tenant -&gt; 404.</t>
         </is>
       </c>
       <c r="L99" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -7029,15 +7029,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I97" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I97" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J97" s="11" t="n"/>
       <c r="K97" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s8_isolation_scenarios.test_brain_chunk_visibility_matrix: _chunk_visible matrix -- owner+team_manage &amp; uploader see all; public-&gt;anyone; dept-&gt;matching department or allow-listed role; private-&gt;allow-listed role only. A user can't see a doc they aren't cleared for.</t>
         </is>
       </c>
       <c r="L97" s="11" t="inlineStr">
@@ -7197,15 +7197,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I100" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I100" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J100" s="11" t="n"/>
       <c r="K100" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s8_isolation_scenarios.test_email_global_unique_and_membership_compound_unique: users.email is globally unique (same email can't back a 2nd tenant's user); memberships are (user_id,tenant_id) compound-unique, but the same user CAN belong to two tenants.</t>
         </is>
       </c>
       <c r="L100" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -6861,15 +6861,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I94" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I94" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J94" s="11" t="n"/>
       <c r="K94" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s8_isolation_scenarios.test_get_current_user_isolation_guards_present: the legacy no-membership fallback is trusted ONLY when the user's own tenant_id == the token's claimed tenant (source-pinned), so a mid-migration token can't cause tenant confusion.</t>
         </is>
       </c>
       <c r="L94" s="11" t="inlineStr">
@@ -7085,15 +7085,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I98" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I98" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J98" s="11" t="n"/>
       <c r="K98" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s8_isolation_scenarios.test_otp_is_keyed_by_phone_and_tenant: otp_codes are keyed by (phone, tenant_id); two tenants sharing a phone get INDEPENDENT rows, never overwriting.</t>
         </is>
       </c>
       <c r="L98" s="11" t="inlineStr">
@@ -7253,15 +7253,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I101" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I101" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J101" s="11" t="n"/>
       <c r="K101" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s8_isolation_scenarios.test_get_current_user_isolation_guards_present: get_current_user refuses a revoked jti (is_revoked) and 403s a suspended user or suspended tenant (source-pinned; is_revoked behavior covered in test_session_revocation).</t>
         </is>
       </c>
       <c r="L101" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -7981,15 +7981,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I114" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I114" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J114" s="11" t="n"/>
       <c r="K114" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s10_concurrency_scenarios.test_stage_version_cas_admits_exactly_one_writer: 8 concurrent stage_version CAS updates -&gt; exactly 1 wins (modified_count sums to 1), version advances exactly once. Single-writer contract holds at runtime.</t>
         </is>
       </c>
       <c r="L114" s="11" t="inlineStr">
@@ -8373,15 +8373,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I121" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I121" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J121" s="11" t="n"/>
       <c r="K121" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s10_concurrency_scenarios.test_auto_invoice_concurrent_double_completion: a serialized re-run never double-books (source_task_id guard holds); documented that the find-then-insert guard has NO unique index, so a true race COULD double-book (1-or-2).</t>
         </is>
       </c>
       <c r="L121" s="11" t="inlineStr">
@@ -8485,15 +8485,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I123" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I123" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J123" s="11" t="n"/>
       <c r="K123" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s10_concurrency_scenarios.test_billing_webhook_idempotency_key_is_unique: 5 concurrent duplicate webhooks -&gt; only 1 accepted, unique index blocks the rest (no double-charge/double-upgrade).</t>
         </is>
       </c>
       <c r="L123" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -8093,15 +8093,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I116" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I116" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J116" s="11" t="n"/>
       <c r="K116" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s10_concurrency_scenarios.test_seat_limit_toctou_over_provisions: worst-case interleaving (all invites run the cap CHECK before any INSERT) -&gt; all 3 pass a cap of 3 with 2 used -&gt; 5 active. CONFIRMED TOCTOU bug (BUG-12); needs an atomic seat reservation.</t>
         </is>
       </c>
       <c r="L116" s="11" t="inlineStr">
@@ -10305,7 +10305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11421,6 +11421,53 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>BUG-12</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Billing / seats</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>enforce_seat_limit COUNTS active memberships then the caller INSERTS, with no atomic reservation between the two. Under concurrent invites at the cap boundary, every request passes the count (all see the same sub-cap number) and then commits -&gt; the workspace over-provisions past its plan's seat cap (proven: 5 active against a cap of 3).</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Flagged (exposed by test; fix = atomic reservation -- e.g. a conditional findOneAndUpdate on a seat counter, or a unique (tenant,seat_index) reservation -- rather than count-then-insert).</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>test_s10_concurrency_scenarios.py</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>T10-10.3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -8205,15 +8205,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I118" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I118" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J118" s="11" t="n"/>
       <c r="K118" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s10_concurrency_scenarios.test_quota_overshoot_without_reservation: two parallel check_quota(cost=60) against a cap of 100 BOTH pass (each sees 0 used) -&gt; collectively burn 120, overshooting. No reservation between check and spend (fail-open aggregate).</t>
         </is>
       </c>
       <c r="L118" s="11" t="inlineStr">
@@ -8261,15 +8261,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I119" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I119" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J119" s="11" t="n"/>
       <c r="K119" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s10_concurrency_scenarios.test_leader_lock_elects_single_holder: 5 replicas try_acquire the same Mongo lock -&gt; exactly 1 wins; the holder can refresh its own lease; a different replica is refused while the lease is live (atomic leader election).</t>
         </is>
       </c>
       <c r="L119" s="11" t="inlineStr">
@@ -8429,15 +8429,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I122" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I122" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J122" s="11" t="n"/>
       <c r="K122" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s10_concurrency_scenarios.test_standalone_payment_expense_idempotency: a serialized re-run never books a second expense (payment_id guard holds); documented that the find-then-insert on payment_id has no unique index so a true race could double-book.</t>
         </is>
       </c>
       <c r="L122" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -8149,15 +8149,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I117" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I117" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J117" s="11" t="n"/>
       <c r="K117" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s10_concurrency_scenarios.test_stage_enter_double_spawn_race: on_stage_enter is find-then-insert on (workflow_id, stage_key) with NO unique index -&gt; worst-case interleaving double-spawns the same template task (proven: 2). See BUG-13.</t>
         </is>
       </c>
       <c r="L117" s="11" t="inlineStr">
@@ -8317,15 +8317,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I120" s="11" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I120" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J120" s="11" t="n"/>
       <c r="K120" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Done -- test_s10_concurrency_scenarios.test_followup_throttle_in_memory_and_escalation_idempotent: the 60s follow-up throttle is a per-process in-memory dict (not shared across workers), so a multi-worker deploy CAN double-run the sweep -- but the escalation ladder's target&lt;=escalation_level guard makes that safe (idempotent).</t>
         </is>
       </c>
       <c r="L120" s="11" t="inlineStr">
@@ -10305,7 +10305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11468,6 +11468,53 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>BUG-13</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Workflow engine / stage tasks</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>on_stage_enter spawns a stage's template tasks with a find({workflow_id,stage_key})-then-insert and NO unique index. A concurrent re-entry (an advance racing a retry, or two ticks) can pass the existence check together and both insert -&gt; duplicate template tasks at the stage (proven under worst-case interleaving).</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Flagged (fix = a unique partial index on (tenant_id, workflow_id, stage_key, template) or an upsert on that key, instead of find-then-insert).</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>test_s10_concurrency_scenarios.py</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>T10-10.4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -8101,7 +8101,7 @@
       <c r="J116" s="11" t="n"/>
       <c r="K116" s="12" t="inlineStr">
         <is>
-          <t>Done -- test_s10_concurrency_scenarios.test_seat_limit_toctou_over_provisions: worst-case interleaving (all invites run the cap CHECK before any INSERT) -&gt; all 3 pass a cap of 3 with 2 used -&gt; 5 active. CONFIRMED TOCTOU bug (BUG-12); needs an atomic seat reservation.</t>
+          <t>Done -- BUG-12 FIXED. test_s10_concurrency_scenarios.test_seat_limit_atomic_reservation: 3 racing reserve_seat() calls for 1 free seat -&gt; exactly 1 admitted, seats_used lands at the cap (never above); releasing frees a seat back. Atomic conditional $inc replaces the count-then-insert.</t>
         </is>
       </c>
       <c r="L116" s="11" t="inlineStr">
@@ -8157,7 +8157,7 @@
       <c r="J117" s="11" t="n"/>
       <c r="K117" s="12" t="inlineStr">
         <is>
-          <t>Done -- test_s10_concurrency_scenarios.test_stage_enter_double_spawn_race: on_stage_enter is find-then-insert on (workflow_id, stage_key) with NO unique index -&gt; worst-case interleaving double-spawns the same template task (proven: 2). See BUG-13.</t>
+          <t>Done -- BUG-13 FIXED. test_s10_concurrency_scenarios.test_stage_enter_double_spawn_is_blocked: a partial unique index over source='engine' tasks makes the second concurrent template-task insert fail (caught + skipped), so on_stage_enter can't double-spawn; ordinary tasks unconstrained.</t>
         </is>
       </c>
       <c r="L117" s="11" t="inlineStr">
@@ -11447,9 +11447,9 @@
           <t>enforce_seat_limit COUNTS active memberships then the caller INSERTS, with no atomic reservation between the two. Under concurrent invites at the cap boundary, every request passes the count (all see the same sub-cap number) and then commits -&gt; the workspace over-provisions past its plan's seat cap (proven: 5 active against a cap of 3).</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>Flagged (exposed by test; fix = atomic reservation -- e.g. a conditional findOneAndUpdate on a seat counter, or a unique (tenant,seat_index) reservation -- rather than count-then-insert).</t>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>Fixed -- added atomic reserve_seat/release_seat (conditional $inc on tenant.seats_used) + recount_seats reconcile in services/plans.py, maintained at the membership choke points (create/update/remove_membership). N racing reservations now admit exactly cap-used; fail-closed on drift.</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -11494,9 +11494,9 @@
           <t>on_stage_enter spawns a stage's template tasks with a find({workflow_id,stage_key})-then-insert and NO unique index. A concurrent re-entry (an advance racing a retry, or two ticks) can pass the existence check together and both insert -&gt; duplicate template tasks at the stage (proven under worst-case interleaving).</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>Flagged (fix = a unique partial index on (tenant_id, workflow_id, stage_key, template) or an upsert on that key, instead of find-then-insert).</t>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>Fixed -- partial UNIQUE index engine_template_task_unique on (tenant_id,workflow_id,stage_key,title) for source='engine' tasks (bootstrap/lifecycle.py) + on_stage_enter now catches DuplicateKeyError and skips. Concurrent re-entry can't double-spawn; ordinary user tasks are unconstrained (partial filter).</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1110,7 +1110,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Epic 10 -- Testing PLANNED. 12 sprints, 154 scenario tasks scoped from a full code map (roles, formulas, modules, tenancy, concurrency). Builds on Epic 1's Testing Plan (phases A-J) + Go-Live Checklist. Execution picked up sprint by sprint; isolation / RBAC / formula / regression-health are the P0 lanes.</t>
+          <t>Epic 10 -- Testing IN EXECUTION. 84/154 scenario tasks Done (55%); Sprints 1, 2, 3, 7, 8, 10 COMPLETE. Full pytest suite: 1281 passed / 1 skipped, deterministic under xdist. Bugs surfaced+fixed by this effort: BUG-11 (finance direction), BUG-12 (seat TOCTOU), BUG-13 (stage double-spawn), BUG-14 (quota aggregate fail-open).</t>
         </is>
       </c>
     </row>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -1229,19 +1229,19 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -1460,19 +1460,19 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -1493,14 +1493,14 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -5407,13 +5407,13 @@
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J68" s="11" t="n"/>
       <c r="K68" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s6_scale.py::test_solo_owner_operating_score_no_crash -- N=1 no divide-by-zero; owner-&gt;company view, lone member-&gt;self.</t>
         </is>
       </c>
       <c r="L68" s="11" t="inlineStr">
@@ -5463,13 +5463,13 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J69" s="11" t="n"/>
       <c r="K69" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s6_scale.py::test_starter_seat_cap_blocks_eleventh -- 11th seat refused 402 at starter cap 10.</t>
         </is>
       </c>
       <c r="L69" s="11" t="inlineStr">
@@ -5519,13 +5519,13 @@
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J70" s="11" t="n"/>
       <c r="K70" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s6_scale.py::test_business_plan_seats_are_unlimited -- 20 members provision freely; unlimited plan never materialises a counter.</t>
         </is>
       </c>
       <c r="L70" s="11" t="inlineStr">
@@ -5575,13 +5575,13 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J71" s="11" t="n"/>
       <c r="K71" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s6_scale.py::test_operating_score_at_thirty_members_scoped -- 30-member roster rolls up (owner+30), no crash.</t>
         </is>
       </c>
       <c r="L71" s="11" t="inlineStr">
@@ -5631,13 +5631,13 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J72" s="11" t="n"/>
       <c r="K72" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s6_scale.py::test_thirty_parallel_task_creates_no_lost_writes -- 30 concurrent inserts all land, no loss/collision.</t>
         </is>
       </c>
       <c r="L72" s="11" t="inlineStr">
@@ -5687,13 +5687,13 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J73" s="11" t="n"/>
       <c r="K73" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s6_scale.py::test_seat_race_at_cap_admits_exactly_free_seats -- 6 racing invites at cap 10 admit exactly the 2 free seats (BUG-12 fix holds at scale).</t>
         </is>
       </c>
       <c r="L73" s="11" t="inlineStr">
@@ -5743,13 +5743,13 @@
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J74" s="11" t="n"/>
       <c r="K74" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s6_scale.py::test_operating_score_at_thirty_members_scoped -- member self-view stays scoped (no team-roster leak); owner view-as scoped to target.</t>
         </is>
       </c>
       <c r="L74" s="11" t="inlineStr">
@@ -5799,13 +5799,13 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J75" s="11" t="n"/>
       <c r="K75" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s6_scale.py::test_quota_walls_pre_block_at_the_cap -- token/storage/brain-doc walls pre-block at cap; surfaced + fixed BUG-14.</t>
         </is>
       </c>
       <c r="L75" s="11" t="inlineStr">
@@ -5855,13 +5855,13 @@
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="J76" s="11" t="n"/>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Invite-OTP flow (7-day expiry / single-use / 30s cooldown) is an auth-flow test needing an SMS-send mock, not a pure scale test -- moved to Sprint 4 (onboarding).</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
@@ -5911,13 +5911,13 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J77" s="11" t="n"/>
       <c r="K77" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s6_scale.py::test_deprovision_at_scale_no_orphans_and_last_owner_guard -- deprovision reassigns tasks (no orphans) + last-owner guard refuses sole-owner removal.</t>
         </is>
       </c>
       <c r="L77" s="11" t="inlineStr">
@@ -10305,7 +10305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10336,7 +10336,7 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>Tally: 10 findings -&gt; 3 Fixed, 6 Flagged (product decisions), 1 Disproven. Plus 4 test-infra/wiring items.</t>
+          <t>Tally: 14 bug findings -&gt; 7 Fixed, 6 Flagged (product decisions), 1 Disproven. Plus 11 test-infra/wiring items (INF-*).</t>
         </is>
       </c>
     </row>
@@ -11512,6 +11512,53 @@
       <c r="I28" s="11" t="inlineStr">
         <is>
           <t>T10-10.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>BUG-14</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Quotas / billing</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>services/quotas.py summed monthly usage with an UN-AWAITED aggregate(). On AsyncMongoClient aggregate() is a coroutine, so `async for row in db.x.aggregate(...)` raised TypeError, which the broad fail-open except swallowed -&gt; usage read as 0. Effect: the llm_tokens_total, stt_minutes AND storage_bytes quota walls NEVER enforced (every read looked under-cap); only brain_docs (count_documents) actually walled. A tenant could blow past their monthly token/storage caps unchecked.</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>test_s6_scale.py::test_quota_walls_pre_block_at_the_cap</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>T10-06.8</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1262,19 +1262,19 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -3733,7 +3733,7 @@
       <c r="J38" s="11" t="n"/>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: Register-flow (mints tenant/owner/membership + runs AI setup) -&gt; best as integration; pair with .9.</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr">
@@ -3783,13 +3783,13 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J39" s="11" t="n"/>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s4_onboarding.py: interview state machine -- Q1 opener industry-aware (OPENERS_WITH_INDUSTRY) + localized OPENER_WHY, MAX-6 hard cap, MIN-2 floor overrides early LLM 'enough', back-step re-opens last Q&amp;A. 4 tests.</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
@@ -3845,7 +3845,7 @@
       <c r="J40" s="11" t="n"/>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: ai_setup_status generated|defaulted|failed + owner retry -&gt; db-tier next (fake the ai_setup generators).</t>
         </is>
       </c>
       <c r="L40" s="11" t="inlineStr">
@@ -3895,13 +3895,13 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J41" s="11" t="n"/>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s4_onboarding.py::test_website_intel_ssrf_block_and_fallback -- internal/loopback/metadata URLs refused 400 pre-fetch; unreachable public URL degrades to {fetched:false} so onboarding continues.</t>
         </is>
       </c>
       <c r="L41" s="11" t="inlineStr">
@@ -3951,13 +3951,13 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J42" s="11" t="n"/>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s4_onboarding.py::test_dpdp_consent_451_gate -- no/stale/revoked consent -&gt; 451 needs_reconsent gate; fresh current-version grant opens it (services/ai_consent.py).</t>
         </is>
       </c>
       <c r="L42" s="11" t="inlineStr">
@@ -4013,7 +4013,7 @@
       <c r="J43" s="11" t="n"/>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: Rate-limit thresholds + CAPTCHA (check_rate_limit) -&gt; db-tier next.</t>
         </is>
       </c>
       <c r="L43" s="11" t="inlineStr">
@@ -4063,13 +4063,13 @@
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J44" s="11" t="n"/>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s4_onboarding.py: draft HMAC token round-trip (tamper/wrong-id/None rejected), valid-step-keys-only persist, resume via get, freeze-on-complete, merge-into-register (client wins). 3 tests.</t>
         </is>
       </c>
       <c r="L44" s="11" t="inlineStr">
@@ -4125,7 +4125,7 @@
       <c r="J45" s="11" t="n"/>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: Duplicate-email race + stub-tenant rollback -&gt; register-flow / integration.</t>
         </is>
       </c>
       <c r="L45" s="11" t="inlineStr">
@@ -4181,7 +4181,7 @@
       <c r="J46" s="11" t="n"/>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: Dept-&gt;role transform is inline in register (auth.py) -&gt; exercise via the .1 register-flow test.</t>
         </is>
       </c>
       <c r="L46" s="11" t="inlineStr">
@@ -4237,7 +4237,7 @@
       <c r="J47" s="11" t="n"/>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: First-login reveal counts -&gt; register-flow.</t>
         </is>
       </c>
       <c r="L47" s="11" t="inlineStr">
@@ -4293,7 +4293,7 @@
       <c r="J48" s="11" t="n"/>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: Per-niche GENERATION QUALITY -&gt; live-LLM golden-set (integration).</t>
         </is>
       </c>
       <c r="L48" s="11" t="inlineStr">
@@ -4349,7 +4349,7 @@
       <c r="J49" s="11" t="n"/>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: Interview QUESTION quality/count -&gt; live-LLM (integration).</t>
         </is>
       </c>
       <c r="L49" s="11" t="inlineStr">
@@ -4405,7 +4405,7 @@
       <c r="J50" s="11" t="n"/>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: Prompt tunability golden-set -&gt; live-LLM harness (integration).</t>
         </is>
       </c>
       <c r="L50" s="11" t="inlineStr">
@@ -4461,7 +4461,7 @@
       <c r="J51" s="11" t="n"/>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: Back-navigate re-answer: state-machine half covered by .2 back-step; full voice re-answer -&gt; browser.</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
@@ -4517,7 +4517,7 @@
       <c r="J52" s="11" t="n"/>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: Refine loop re-blueprints -&gt; live-LLM (integration).</t>
         </is>
       </c>
       <c r="L52" s="11" t="inlineStr">
@@ -4573,7 +4573,7 @@
       <c r="J53" s="11" t="n"/>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: Full onboarding journey -&gt; browser-driven.</t>
         </is>
       </c>
       <c r="L53" s="11" t="inlineStr">
@@ -4629,7 +4629,7 @@
       <c r="J54" s="11" t="n"/>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: First-impression 'feeling' UX -&gt; browser heuristic review.</t>
         </is>
       </c>
       <c r="L54" s="11" t="inlineStr">
@@ -4685,7 +4685,7 @@
       <c r="J55" s="11" t="n"/>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Grounded in code map 2026-08-29 | TIER: Voice-capture UX -&gt; browser + Sarvam STT.</t>
         </is>
       </c>
       <c r="L55" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1262,14 +1262,14 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -3789,7 +3789,7 @@
       <c r="J39" s="11" t="n"/>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>test_s4_onboarding.py: interview state machine -- Q1 opener industry-aware (OPENERS_WITH_INDUSTRY) + localized OPENER_WHY, MAX-6 hard cap, MIN-2 floor overrides early LLM 'enough', back-step re-opens last Q&amp;A. 4 tests.</t>
+          <t>test_s4_onboarding.py: interview state machine -- Q1 opener industry-aware (OPENERS_WITH_INDUSTRY) + localized OPENER_WHY, MAX-6 hard cap, MIN-2 floor overrides early LLM 'enough', back-step re-opens last Q&amp;A. 4 tests. | LIVE-UI VERIFIED (browser preview, localhost:3000): Q1 opener rendered 'HI RAVI -- I CAN SEE WEAVE CO IS IN TEXTILE &amp; APPAREL...' (industry-aware, localized why); follow-up Q2 grounded in the answer ('weaving and dyeing floor'), no industry re-ask -- improved INTERVIEW prompt confirmed end-to-end.</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
@@ -3839,13 +3839,13 @@
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J40" s="11" t="n"/>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: ai_setup_status generated|defaulted|failed + owner retry -&gt; db-tier next (fake the ai_setup generators).</t>
+          <t>test_s4_onboarding.py: ai_setup status classification (generated|defaulted|failed via _is_meaningful gate) + summarize_ai_setup_status + owner retry re-runs ONLY non-generated (idempotent). 3 tests.</t>
         </is>
       </c>
       <c r="L40" s="11" t="inlineStr">
@@ -4007,13 +4007,13 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J43" s="11" t="n"/>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: Rate-limit thresholds + CAPTCHA (check_rate_limit) -&gt; db-tier next.</t>
+          <t>test_s4_onboarding.py: sliding-window rate limit admits to cap then refuses (Retry-After&gt;0, independent buckets) + signup guard enforces the 5/10s burst ceiling with 429. 2 tests.</t>
         </is>
       </c>
       <c r="L43" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1262,14 +1262,14 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -4567,13 +4567,13 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J53" s="11" t="n"/>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: Full onboarding journey -&gt; browser-driven.</t>
+          <t>LIVE browser-driven full onboarding journey (localhost:3000 + backend :8001): Basics -&gt; Your world (industry) -&gt; Interview (industry-aware opener + grounded adaptive Qs, MIN2/MAX6) -&gt; Blueprint reveal (grounded 4 depts / 8 tasks / 3 approvals) -&gt; Register (owner+tenant created, plan=trial) -&gt; landed in the app Desk as owner. Surfaced+fixed BUG-15 (phantom '0 Workflows' stat). Also caught: register rejects reserved-TLD emails (.test) with 422 -- correct validation.</t>
         </is>
       </c>
       <c r="L53" s="11" t="inlineStr">
@@ -10305,7 +10305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10336,7 +10336,7 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>Tally: 14 bug findings -&gt; 7 Fixed, 6 Flagged (product decisions), 1 Disproven. Plus 11 test-infra/wiring items (INF-*).</t>
+          <t>Tally: 15 bug findings -&gt; 8 Fixed, 6 Flagged (product decisions), 1 Disproven. Plus 11 test-infra/wiring items (INF-*).</t>
         </is>
       </c>
     </row>
@@ -11559,6 +11559,53 @@
       <c r="I29" s="11" t="inlineStr">
         <is>
           <t>T10-06.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>BUG-15</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Onboarding / reveal</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>The onboarding 'Your OS' reveal (frontend BuildReveal.js) showed a stat card counting bp.workflows -&gt; ALWAYS 0 for every new founder on the first-impression screen. Root cause: WE-02 (2026-08-16) retired the blueprint's 'workflows' key -- normalize_os_blueprint (shared/normalizers.py) no longer returns it; operating_model.pipelines is the single source of truth for pipelines, and it's generated at register time, not at preview. The reveal was never updated, so it advertised '0 Workflows' to every founder. Surfaced by driving the full onboarding flow in the browser preview.</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>browser-driven (BuildReveal.js reveal); T10-04.16</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>T10-04.16</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1262,14 +1262,14 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -3727,13 +3727,13 @@
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J38" s="11" t="n"/>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: Register-flow (mints tenant/owner/membership + runs AI setup) -&gt; best as integration; pair with .9.</t>
+          <t>test_s4_register.py::test_register_full_happy_path_and_reveal_counts -- register provisions a trial tenant + owner user + owner membership (all perms, active), records AI setup (lexicon/operating_model/finance generated) + pre-granted DPDP consent; returns token + os_summary.</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr">
@@ -4119,13 +4119,13 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J45" s="11" t="n"/>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: Duplicate-email race + stub-tenant rollback -&gt; register-flow / integration.</t>
+          <t>test_s4_register.py::test_duplicate_email_sequential_and_concurrent_no_orphan -- a 2nd register with an existing email -&gt; 400 (no 2nd tenant); concurrent same-email race (real unique index) -&gt; exactly 1 wins, loser gets clean 400 + rolls back its tenant (no orphan).</t>
         </is>
       </c>
       <c r="L45" s="11" t="inlineStr">
@@ -4175,13 +4175,13 @@
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J46" s="11" t="n"/>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: Dept-&gt;role transform is inline in register (auth.py) -&gt; exercise via the .1 register-flow test.</t>
+          <t>test_s4_register.py::test_register_departments_become_clean_roles -- owner role stripped (implicit for creator), duplicate keys collapse, blank labels humanized; result = distinct assignable roles.</t>
         </is>
       </c>
       <c r="L46" s="11" t="inlineStr">
@@ -4231,13 +4231,13 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J47" s="11" t="n"/>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: First-login reveal counts -&gt; register-flow.</t>
+          <t>test_s4_register.py::test_register_full_happy_path_and_reveal_counts -- os_summary reveal counts (departments/operational_tasks/approval_rules) match the generated tenant fields exactly.</t>
         </is>
       </c>
       <c r="L47" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1262,14 +1262,14 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -3789,7 +3789,7 @@
       <c r="J39" s="11" t="n"/>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>test_s4_onboarding.py: interview state machine -- Q1 opener industry-aware (OPENERS_WITH_INDUSTRY) + localized OPENER_WHY, MAX-6 hard cap, MIN-2 floor overrides early LLM 'enough', back-step re-opens last Q&amp;A. 4 tests. | LIVE-UI VERIFIED (browser preview, localhost:3000): Q1 opener rendered 'HI RAVI -- I CAN SEE WEAVE CO IS IN TEXTILE &amp; APPAREL...' (industry-aware, localized why); follow-up Q2 grounded in the answer ('weaving and dyeing floor'), no industry re-ask -- improved INTERVIEW prompt confirmed end-to-end.</t>
+          <t>test_s4_onboarding.py: interview state machine -- Q1 opener industry-aware (OPENERS_WITH_INDUSTRY) + localized OPENER_WHY, MAX-6 hard cap, MIN-2 floor overrides early LLM 'enough', back-step re-opens last Q&amp;A. 4 tests. | LIVE-UI VERIFIED (browser preview, localhost:3000): Q1 opener rendered 'HI RAVI -- I CAN SEE WEAVE CO IS IN TEXTILE &amp; APPAREL...' (industry-aware, localized why); follow-up Q2 grounded in the answer ('weaving and dyeing floor'), no industry re-ask -- improved INTERVIEW prompt confirmed end-to-end. | ALL 11 LANGUAGES verified: pytest test_q1_opener_localized_across_all_languages (opener template + localized why per lang) + LIVE via the running backend API (all 11 return the correct native-script industry-aware opener + localized why; batch also re-confirmed the 5/10s burst 429). Tamil rendered end-to-end in the real interview UI.</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
@@ -4455,13 +4455,13 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J51" s="11" t="n"/>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: Back-navigate re-answer: state-machine half covered by .2 back-step; full voice re-answer -&gt; browser.</t>
+          <t>LIVE browser-driven (localhost:3000): answered Q1 in the Tamil interview -&gt; Q2, clicked Back -&gt; returned to Q1 with the PRIOR answer pre-filled and editable; re-answered with different content (dyeing/grey-cloth/local-shops, no exports) -&gt; transcript updated and the new Q2 was grounded in the EDITED answer, the saree/export framing gone. The founder-described back-and-re-answer scenario works end to end.</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
@@ -4623,13 +4623,13 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J54" s="11" t="n"/>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: First-impression 'feeling' UX -&gt; browser heuristic review.</t>
+          <t>First-impression heuristic (live, 2 full runs EN + 1 TA): smooth step transitions; warm personalized copy ('who's running Weave Co?', 'Nice to meet you, Ravi'); loading states ('warming up...', 'Dex is building... 43%' with progress creep + rotating status lines); clear stepper + 'Question N up to 6'; voice-first multilingual (11 langs, native script, Read/listen); grounded reveal quoting the founder's own words. PASS. Minor polish nits: (a) Basics 'Continue' shifts up when the helper hint disappears on typing -&gt; can cause a misclick; (b) Desk welcome heading wraps oddly ('Welcome, Ravi.  from  here.').</t>
         </is>
       </c>
       <c r="L54" s="11" t="inlineStr">
@@ -4679,13 +4679,13 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J55" s="11" t="n"/>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: Voice-capture UX -&gt; browser + Sarvam STT.</t>
+          <t>Voice-capture UX (browser preview, no real mic): 'Speak' affordance present on every question and correctly requests microphone permission on tap; when the mic is unavailable/blocked the UI GRACEFULLY FALLS BACK to typing -- input + Answer/Back/Skip stay usable, no crash. Live-device parts (recording indicator, transcription latency, Tanglish/accent handling, retry-on-failed-transcription) require a real mic + Sarvam STT round-trip and can't be exercised in a headless preview -&gt; covered by the live-integration lane, not here.</t>
         </is>
       </c>
       <c r="L55" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1262,19 +1262,19 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -4287,13 +4287,13 @@
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J48" s="11" t="n"/>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: Per-niche GENERATION QUALITY -&gt; live-LLM golden-set (integration).</t>
+          <t>evals/cases/onboarding.py (run: python -m evals.run --domain onboarding [--live]). Per-niche OS GENERATION QUALITY golden set -- 5 personas (restaurant/clinic/cold-chain/textile/retail), each runs the REAL generate_blueprint (services/ai/onboarding.py, extracted from signup) with shape + GROUNDING checks (founder's real nouns must appear; no 'owner' dept; welcome line). Replay 5/5 (free/CI via test_epic3_s1_evals) AND --live 5/5 -- the real sonnet-4-6 grounds every niche correctly.</t>
         </is>
       </c>
       <c r="L48" s="11" t="inlineStr">
@@ -4343,13 +4343,13 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J49" s="11" t="n"/>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: Interview QUESTION quality/count -&gt; live-LLM (integration).</t>
+          <t>evals/cases/onboarding.py (run: python -m evals.run --domain onboarding [--live]). Interview QUESTION quality -- next_interview_question golden cases: mid-interview asks ONE short (&lt;=30w) grounded question with enough=false below MIN; end-depth case pins the ends-OR-asks invariant. Replay 2/2 + --live 2/2. LIVE FINDING (sonnet-4-6): the model is CONSERVATIVE about ending -- on a clear 3-answer clinic it kept asking rather than ending early, i.e. the interview leans toward MAX. Tuning target for .13.</t>
         </is>
       </c>
       <c r="L49" s="11" t="inlineStr">
@@ -4399,13 +4399,13 @@
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J50" s="11" t="n"/>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: Prompt tunability golden-set -&gt; live-LLM harness (integration).</t>
+          <t>evals/cases/onboarding.py (run: python -m evals.run --domain onboarding [--live]). Prompt-tunability / no-regression harness = the onboarding golden set itself, wired into the existing evals framework (Epic 3 E3-01.4): replay runs in CI (test_epic3_s1_evals) and catches SHAPE regressions on any prompt/model change for free; --live re-runs the same personas against the real model to diff QUALITY drift. Open tuning item captured: soften the INTERVIEW prompt's end-early guidance (see .12 live finding).</t>
         </is>
       </c>
       <c r="L50" s="11" t="inlineStr">
@@ -4511,13 +4511,13 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J52" s="11" t="n"/>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29 | TIER: Refine loop re-blueprints -&gt; live-LLM (integration).</t>
+          <t>evals/cases/onboarding.py (run: python -m evals.run --domain onboarding [--live])::refine_adds_returns_workflow. Refine loop -- generate_blueprint with a post-draft founder correction ('add returns/exchange') must surface a returns dept/task/approval. Replay + --live both PASS (real model incorporates the refinement). The signup /interview/refine endpoint re-runs this same function.</t>
         </is>
       </c>
       <c r="L52" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -1493,14 +1493,14 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -5855,13 +5855,13 @@
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>Deferred</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J76" s="11" t="n"/>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>Invite-OTP flow (7-day expiry / single-use / 30s cooldown) is an auth-flow test needing an SMS-send mock, not a pure scale test -- moved to Sprint 4 (onboarding).</t>
+          <t>test_s6_invite_otp.py (5 tests): invite 7-day expiry (410 past window) + single-use consumption (OTP verify nulls invite_token -&gt; link 404s); OTP 30s resend cooldown scoped per (phone, tenant) so a cooldown in one workspace never locks the phone out of another; multi-tenant ambiguity sends NO OTP + leaks no tenant (verify without hint -&gt; 409); OTP single-use + 5-attempt lockout (429) + TTL expiry; 30 concurrent invites -&gt; 30 independent OTP rows, all verify in their own tenant, all consumed, 0 leftover. SMS/APM gateway mocked to a known code. -&gt; Sprint 6 COMPLETE (10/10).</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
@@ -8599,13 +8599,13 @@
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J125" s="11" t="n"/>
       <c r="K125" s="12" t="inlineStr">
         <is>
-          <t>SCOPED + Phase-1 spike DONE (2026-08-29). Landscape: 55/141 test files are live-integration (HTTP via requests); 45 default to the HOSTED preview URL (safety risk: silent writes to a shared remote env), 12 hard-require the env (the collection errors). App DB = MONGO_URL+DB_NAME env; bootstrap self-seeds admin@decisionos.biz + the Sharma demo (owner@sharma.com) = exactly the identities the tests log in as. HARNESS BUILT: tests/_live_harness.py boots uvicorn on an ISOLATED db (dos_test_live_*, never founder-os-58), pins creds/AUTH_RETURN_TOKEN/COOKIE_SECURE, waits for seed via DIRECT DB-poll (NOT login-poll -- that trips the brute-force rate limiter), runs, then drops the db. Proof: test_iteration60_admin.py 16/16 green end-to-end. PHASES: P1 harness [DONE] -&gt; P2 kill the 45 hosted-preview URL defaults (fail-closed base_url helper) -&gt; P3 determinism (seed-vs-clean assumptions, cross-file writes under -n, the /app/memory WinError, per-file stale assertions like the ai-keys set) -&gt; P4 @integration/@unit markers + CI gate (feeds T10-11.5/11.4) -&gt; P5 (optional) in-process ASGI for the hottest files. || P2 DONE (2026-08-29): added tests/integration_base.base_url() -- one env-only, fail-closed source; repointed all 55 HTTP integration files off their hosted-preview / frontend-.env defaults. Unset env now SKIPS the module (55 skipped) instead of erroring or silently hitting a shared remote. Also repointed 2 stale `motor` imports -&gt; pymongo. Canonical xdist suite: 1207 passed / 15 failed / 0 errors (was 88 BACKEND_URL errors); the 15 are the pre-existing offline-behavioral tail (ai_consent, onboarding_flow, epic3_*, quotas) unrelated to P2. Next: P3 determinism/assertions, P4 markers+CI. || P4 DONE (2026-08-29): convention-based tiering (conftest) + .github/workflows/tests.yml (unit gate blocking; db + integration best-effort) + backend/tests/README.md. Full suite 1222 pass, unit gate 1200 pass offline.</t>
+          <t>No pre-existing iteration_* FAILURES remain -- cleared by INF-11 (stale `from server import X` repointed to the Epic-8 modules; onboarding_flow patches retargeted to services.ai.generators; epic3 s5/s9/s10 migrated to with_test_db on an isolated DB). Full suite green (1314 passed / 1 skipped); iteration_* either pass or skip cleanly where they need live infra. No failing assertions left to fix.</t>
         </is>
       </c>
       <c r="L125" s="11" t="inlineStr">
@@ -8879,13 +8879,13 @@
       </c>
       <c r="I130" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J130" s="11" t="n"/>
       <c r="K130" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Coverage tooling WIRED: pytest-cov==5.0.0 + coverage==7.16.0 (requirements-dev.txt) + .coveragerc (high-risk source list + floors). Baseline: services.operating_score = 52% (floor 50%) via its focused unit tests. CONSTRAINT (real finding): coverage does NOT compose with the suite's -n2 --dist loadscope (pytest-cov x xdist -&gt; 357 spurious failures), and collecting many shim-heavy files single-process trips their module-isolation; so coverage is measured per-module/per-area, single-process (-o addopts=""). Floors for permissions/tenancy/ingestion/ledger are TBD -- they're exercised only indirectly across shim-isolated files; the follow-up is a per-area coverage suite that groups non-conflicting tests.</t>
         </is>
       </c>
       <c r="L130" s="11" t="inlineStr">
@@ -8935,13 +8935,13 @@
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J131" s="11" t="n"/>
       <c r="K131" s="12" t="inlineStr">
         <is>
-          <t>In progress: triaged the 27 source-grep suites -&gt; 9 fixed. Remaining tail categorized in Bug Log INF-06 (event-loop harness) + INF-07 (mixed shim + possibly-real behavioural fake-DB failures). | 2026-08-29: event-loop flakiness eliminated -- 14 files converted off get_event_loop()/stale-patch to dedicated per-module loops; +118 tests deterministic. Remaining non-determinism is env-gated (REACT_APP_BACKEND_URL / live server) = T10-11.2.</t>
+          <t>Environmental/flaky failures catalogued + fixed as INF-06 (event-loop harness: per-module new_event_loop), INF-07 (resolve_wa_tenant), INF-08 (tenancy_hygiene stale tests), INF-11 (15 offline + 8 shim-fragility). Determinism: the suite is stable across repeated full runs under -n2 --dist loadscope (module-scoped so no cross-worker event-loop sharing; db-tier tests use isolated with_test_db). Zero-flake on the current tree.</t>
         </is>
       </c>
       <c r="L131" s="11" t="inlineStr">
@@ -8991,13 +8991,13 @@
       </c>
       <c r="I132" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J132" s="11" t="n"/>
       <c r="K132" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>tests/factories.py: reusable per-niche test-data factory. build_niche_tenant(db, niche) assembles a realistic tenant (owner+team, contacts, sales+purchase invoices, in/out payments, tasks) for 5 niches (textile/logistics/restaurant/clinic/retail), deterministic, shaped to the real read paths. test_s11_infra.py proves all 5 build + a factory tenant feeds operating_score (finance sub-score reads only direction=in payments, per BUG-11). Powers S5 (niche) + S6 (scale).</t>
         </is>
       </c>
       <c r="L132" s="11" t="inlineStr">
@@ -9047,13 +9047,13 @@
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J133" s="11" t="n"/>
       <c r="K133" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Post-sprint regression baseline discipline: the FULL pytest suite is re-run after every sprint before the commit that merges it to Backend_optimization, and the pass count is tracked in each sprint's commit + this tracker (current baseline: 1314 passed / 1 skipped, 2026-09-01). The parked .github/workflows/tests.yml automates this as a blocking unit gate once pushed (after Phase 1).</t>
         </is>
       </c>
       <c r="L133" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1295,19 +1295,19 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -4735,13 +4735,13 @@
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J56" s="11" t="n"/>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_textile_baseline_full_flow -- factory textile tenant: owner company operating-score view + finance chases a 30-day-overdue receivable. The regression baseline niche.</t>
         </is>
       </c>
       <c r="L56" s="11" t="inlineStr">
@@ -4791,13 +4791,13 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J57" s="11" t="n"/>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_logistics_roles_distinct_no_textile_leak -- logistics tenant has dispatch/fleet/compliance roles, industry 'Logistics &amp; Transport', NO textile terms leak. AI-gen distinctness: evals/cases/onboarding.py (golden set, replay+--live) niche_cold_chain.</t>
         </is>
       </c>
       <c r="L57" s="11" t="inlineStr">
@@ -4847,13 +4847,13 @@
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J58" s="11" t="n"/>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_electronics_bom_and_asset_amounts -- manufacturer: component/BOM purchase bills + high-value finished-goods invoice track amount-amount_paid.</t>
         </is>
       </c>
       <c r="L58" s="11" t="inlineStr">
@@ -4903,13 +4903,13 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J59" s="11" t="n"/>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_restaurant_high_volume_cash_no_invoice -- 80 small standalone cash payments with no invoice; operating score renders (no divide-by-zero on cash-heavy data). AI-gen: evals/cases/onboarding.py (golden set, replay+--live) niche_restaurant.</t>
         </is>
       </c>
       <c r="L59" s="11" t="inlineStr">
@@ -4959,13 +4959,13 @@
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J60" s="11" t="n"/>
       <c r="K60" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_clinic_non_sales_model_no_crash -- clinic has no 'sales' role (non-sales, appointment-driven); operating score renders. AI-gen: evals/cases/onboarding.py (golden set, replay+--live) niche_clinic.</t>
         </is>
       </c>
       <c r="L60" s="11" t="inlineStr">
@@ -5015,13 +5015,13 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J61" s="11" t="n"/>
       <c r="K61" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_retail_high_volume_outstanding_aggregation -- 60 overdue receivables aggregate; outstanding sums correctly at volume.</t>
         </is>
       </c>
       <c r="L61" s="11" t="inlineStr">
@@ -5071,13 +5071,13 @@
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J62" s="11" t="n"/>
       <c r="K62" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_pharma_gst_gross_handled_as_is -- GST-inclusive gross invoice (236000 = 200000 + 18%): outstanding = gross - paid, GST not split (no GST math, as designed).</t>
         </is>
       </c>
       <c r="L62" s="11" t="inlineStr">
@@ -5127,13 +5127,13 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J63" s="11" t="n"/>
       <c r="K63" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_consulting_retainers_no_inventory -- services business: recurring retainer/project sales invoices, ZERO purchase bills (no inventory); operating score renders.</t>
         </is>
       </c>
       <c r="L63" s="11" t="inlineStr">
@@ -5183,13 +5183,13 @@
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J64" s="11" t="n"/>
       <c r="K64" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_construction_milestone_partial_payments -- 10,00,000 contract with a 3,00,000 staged milestone -&gt; outstanding = 7,00,000 (partial-payment matching).</t>
         </is>
       </c>
       <c r="L64" s="11" t="inlineStr">
@@ -5239,13 +5239,13 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J65" s="11" t="n"/>
       <c r="K65" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_agriculture_seasonal_gaps_no_misfire -- a 200-day-overdue seasonal receivable is chased; a not-yet-due one does NOT misfire across the seasonal gap.</t>
         </is>
       </c>
       <c r="L65" s="11" t="inlineStr">
@@ -5295,13 +5295,13 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J66" s="11" t="n"/>
       <c r="K66" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_custom_other_industry_no_crash (free-text industry stored as-is, operating score + finance work, no crash) + evals/cases/onboarding.py (golden set, replay+--live) niche_custom_other (real model designs a coherent sourcing/assembly/QA OS for a non-enum industry).</t>
         </is>
       </c>
       <c r="L66" s="11" t="inlineStr">
@@ -5351,13 +5351,13 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J67" s="11" t="n"/>
       <c r="K67" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>test_s5_niches.py::test_all_niches_are_distinct -- all 10 factory niches build with distinct industries + varied role signatures (&gt;=7 distinct); no niche reuses the textile role template. Per-niche generation distinctness gate: evals/cases/onboarding.py (golden set, replay+--live) (6 distinct niche blueprints).</t>
         </is>
       </c>
       <c r="L67" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -4741,7 +4741,7 @@
       <c r="J56" s="11" t="n"/>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>test_s5_niches.py::test_textile_baseline_full_flow -- factory textile tenant: owner company operating-score view + finance chases a 30-day-overdue receivable. The regression baseline niche.</t>
+          <t>test_s5_niches.py::test_textile_baseline_full_flow -- factory textile tenant: owner company operating-score view + finance chases a 30-day-overdue receivable. The regression baseline niche. | REAL END-TO-END (test_s5_e2e_flow.py::test_bill_to_match_to_approve_to_done_to_score): drives the actual chain -- payment auto-MATCHES the invoice via routers.ledger.reconcile_payment (invoice-&gt;paid, applied=42000), decision APPROVED via routers.decisions.approve_decision UNBLOCKS its blocked task (blocked-&gt;todo), task-&gt;done, operating_score reflects. Not just isolated reads.</t>
         </is>
       </c>
       <c r="L56" s="11" t="inlineStr">
@@ -5357,7 +5357,7 @@
       <c r="J67" s="11" t="n"/>
       <c r="K67" s="12" t="inlineStr">
         <is>
-          <t>test_s5_niches.py::test_all_niches_are_distinct -- all 10 factory niches build with distinct industries + varied role signatures (&gt;=7 distinct); no niche reuses the textile role template. Per-niche generation distinctness gate: evals/cases/onboarding.py (golden set, replay+--live) (6 distinct niche blueprints).</t>
+          <t>test_s5_niches.py::test_all_niches_are_distinct -- all 10 factory niches build with distinct industries + varied role signatures (&gt;=7 distinct); no niche reuses the textile role template. Per-niche generation distinctness gate: evals/cases/onboarding.py (golden set, replay+--live) (6 distinct niche blueprints). | REAL DIFFERENTIATION (test_s5_generation_differentiation.py, live-gated RUN_LIVE_LLM=1): runs the ACTUAL ai_generate_operating_model for 4 niches (textile/logistics/restaurant/clinic) and asserts DISTINCT pipeline signatures + niche-specific stages (textile dyeing, logistics transit/storage, restaurant kitchen, clinic appointment) -- only 'procurement' shared. Verified 2026-09-01: 4/4 distinct. (test_s5_niches distinctness only checked hand-seeded factory roles -- this checks the model.)</t>
         </is>
       </c>
       <c r="L67" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1493,19 +1493,19 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -8879,13 +8879,13 @@
       </c>
       <c r="I130" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J130" s="11" t="n"/>
       <c r="K130" s="12" t="inlineStr">
         <is>
-          <t>Coverage tooling WIRED: pytest-cov==5.0.0 + coverage==7.16.0 (requirements-dev.txt) + .coveragerc (high-risk source list + floors). Baseline: services.operating_score = 52% (floor 50%) via its focused unit tests. CONSTRAINT (real finding): coverage does NOT compose with the suite's -n2 --dist loadscope (pytest-cov x xdist -&gt; 357 spurious failures), and collecting many shim-heavy files single-process trips their module-isolation; so coverage is measured per-module/per-area, single-process (-o addopts=""). Floors for permissions/tenancy/ingestion/ledger are TBD -- they're exercised only indirectly across shim-isolated files; the follow-up is a per-area coverage suite that groups non-conflicting tests.</t>
+          <t>Coverage wired + gated. scripts/coverage_highrisk.py runs single-process (pytest-cov does NOT compose with -n2 loadscope) and ENFORCES a floor: services.operating_score = 52% (floor 50%, OK) -- the highest-risk module (BUG-01/BUG-11 lived here). .coveragerc holds the config + floors. The other 4 high-risk modules are documented-blocked (not silently dropped): core.permissions crashes pytest-cov via bcrypt/PyO3 'init once'; services.tenancy/ingestion + routers.ledger have NO isolated db-tier tests -- they're exercised only through the integration tier (test_iteration55_ledger, test_s2_functional), so their coverage needs `coverage run` against the live server, not the offline unit suite. Per-sprint tracking = run the gate script.</t>
         </is>
       </c>
       <c r="L130" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -9663,13 +9663,13 @@
       </c>
       <c r="I144" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J144" s="11" t="n"/>
       <c r="K144" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Browser-verified (owner, karma UI): New Task button opens its modal; Desk stat-cards deep-link (overdue-&gt;my-work, complaints-&gt;inbox); nav pills/dock route correctly. NB: earlier 'dead button' impressions were a test-harness artifact (emulated 1280 viewport scaled into the ~800px pane -&gt; coord clicks missed); a real click opens the modal. Representative, not an exhaustive every-button sweep.</t>
         </is>
       </c>
       <c r="L144" s="11" t="inlineStr">
@@ -9719,13 +9719,13 @@
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J145" s="11" t="n"/>
       <c r="K145" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Browser-verified: New Task form -- proper fields (title/desc/type=Weaving&amp;Production from the onboarded model/assignee/priority/due/approval+proof/file). On-submit validation shows a CLEAR inline error 'Task title is required' (names the field, not just 'invalid'); dialog stays open, NO silent failure. Representative form; CRM + Settings forms exist and follow the same modal pattern.</t>
         </is>
       </c>
       <c r="L145" s="11" t="inlineStr">
@@ -9775,13 +9775,13 @@
       </c>
       <c r="I146" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J146" s="11" t="n"/>
       <c r="K146" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Browser-verified: /desk /crm /my-work /finance /operating-score /settings all load, no white screens. Desktop = top pill-nav (Decision Desk/My Work/Ops/CRM/Team/Dex/Finance); mobile = bottom dock (Desk/Work/Money/More). Deep links + stat-card routes work.</t>
         </is>
       </c>
       <c r="L146" s="11" t="inlineStr">
@@ -9831,13 +9831,13 @@
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J147" s="11" t="n"/>
       <c r="K147" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Browser-verified: real empty states everywhere -- CRM 'No relationships yet' + CTA; My Work 'You're all caught up! / tasks appear once decisions approved'; operating-score 'Score kicks in soon' + 2-step activation; Desk 'No decisions waiting on you'. Loading states present (finance 'Loading...'; mobile bare 'LOADING...' -- functional but unpolished).</t>
         </is>
       </c>
       <c r="L147" s="11" t="inlineStr">
@@ -9887,13 +9887,13 @@
       </c>
       <c r="I148" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J148" s="11" t="n"/>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Browser-verified at 375 (mobile) + 1280 (desktop): mobile Desk = 2x2 cards, dock, NO horizontal overflow; desktop = pill-nav + card grid. MINOR: at the ~800px tablet boundary the nav shell flips at slightly different breakpoints across pages (dock on Desk/CRM vs pill-nav on operating-score) -- a transient tablet-width inconsistency.</t>
         </is>
       </c>
       <c r="L148" s="11" t="inlineStr">
@@ -9943,13 +9943,13 @@
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J149" s="11" t="n"/>
       <c r="K149" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>PARTIAL/BLOCKED: role-gated UI per persona needs finance/sales/ops LOGINS, but the app onboards members via an OTP invite (phone/SMS) -- can't complete a member login in the headless preview without SMS or DEV_OTP_IN_RESPONSE. Backend RBAC (allow/deny, money-column stripping, owner-only gates) is already covered by Sprint 3. Next: enable dev-OTP or seed a member session cookie, then log in as each role and diff the visible tabs/actions.</t>
         </is>
       </c>
       <c r="L149" s="11" t="inlineStr">
@@ -9999,13 +9999,13 @@
       </c>
       <c r="I150" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J150" s="11" t="n"/>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Browser-verified: karma design consistent across pages -- serif display headings, indigo primary actions, flat glass surfaces, dark dock/pill-nav, consistent card/chip patterns. Onboarded roles/model flow through (Task type 'Weaving &amp; Production', roles in Settings). MINOR: CRM shows a black 'Add contact' AND an indigo 'Add your first buyer' for the same action.</t>
         </is>
       </c>
       <c r="L150" s="11" t="inlineStr">
@@ -10055,13 +10055,13 @@
       </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J151" s="11" t="n"/>
       <c r="K151" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>PARTIAL: per-persona journeys -- navigation, form-open, and validation are verified in the REAL UI, but a full create-&gt;persist-&gt;on-screen journey (e.g. create a task and see it land) was flaky to drive via automation (React controlled-input + modal timing; coord clicks miss under viewport scaling). The forms demonstrably work (open + validate); a stable driver (Playwright) or a manual pass is needed to assert each on-screen result end to end.</t>
         </is>
       </c>
       <c r="L151" s="11" t="inlineStr">
@@ -10111,13 +10111,13 @@
       </c>
       <c r="I152" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J152" s="11" t="n"/>
       <c r="K152" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>PARTIAL: Dex/voice UI surfaces present -- the Dex orb button exists, the capture bar renders ('Or capture a decision right here' + Capture on operating-score). But actual voice record/stop + the 'Dex is structuring N' inflight async states can't be driven -- the preview blocks microphone capture. Visual surfaces verified; the live async pipeline states need a real mic / manual pass.</t>
         </is>
       </c>
       <c r="L152" s="11" t="inlineStr">
@@ -10167,13 +10167,13 @@
       </c>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J153" s="11" t="n"/>
       <c r="K153" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Browser-verified: fresh loads are clean -- all /api/ calls 200 (notifications/brief/desk/auth-me/operating-score/tasks/ledger). The earlier console 401s were STALE, accumulated during the backend restart window; a clean reload shows no failing calls.</t>
         </is>
       </c>
       <c r="L153" s="11" t="inlineStr">
@@ -10223,13 +10223,13 @@
       </c>
       <c r="I154" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J154" s="11" t="n"/>
       <c r="K154" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Browser-verified: the app is intentionally SINGLE-THEME (light glass). No theme toggle; emulating prefers-color-scheme:dark produces NO change (renders identical). So no dark theme to break, no theme-only unreadable text. Key flows render correctly in the in-app browser pane.</t>
         </is>
       </c>
       <c r="L154" s="11" t="inlineStr">
@@ -10279,13 +10279,13 @@
       </c>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J155" s="11" t="n"/>
       <c r="K155" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Browser-verified (in-browser a11y P0s): 0 icon-only controls missing an accessible name (all buttons/links have text or aria-label/title); ':focus-visible' CSS present (visible focus rings). Full keyboard-activation-of-every-control + contrast audit would need a dedicated pass, but the P0 basics hold.</t>
         </is>
       </c>
       <c r="L155" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1110,10 +1110,11 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Epic 10 -- Testing IN EXECUTION. 84/154 scenario tasks Done (55%); Sprints 1, 2, 3, 7, 8, 10 COMPLETE. Full pytest suite: 1281 passed / 1 skipped, deterministic under xdist. Bugs surfaced+fixed by this effort: BUG-11 (finance direction), BUG-12 (seat TOCTOU), BUG-13 (stage double-spawn), BUG-14 (quota aggregate fail-open).</t>
-        </is>
-      </c>
-    </row>
+          <t>Epic 10 -- Testing IN EXECUTION. 131/154 scenario tasks Done (85%); Sprints 1-8, 10, 11 COMPLETE (11 sprints), Sprint 13 at 11/12. Remaining: S9 (AI/extraction) + S12 (E2E journeys). Full pytest suite: 1327 passed / 3 skipped, deterministic under xdist. Bugs surfaced+fixed by this effort: BUG-11 (finance direction), BUG-12 (seat TOCTOU), BUG-13 (stage double-spawn), BUG-14 (quota aggregate fail-open), BUG-15 (phantom '0 Workflows' reveal stat).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1559,14 +1560,14 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -9943,13 +9944,13 @@
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J149" s="11" t="n"/>
       <c r="K149" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL/BLOCKED: role-gated UI per persona needs finance/sales/ops LOGINS, but the app onboards members via an OTP invite (phone/SMS) -- can't complete a member login in the headless preview without SMS or DEV_OTP_IN_RESPONSE. Backend RBAC (allow/deny, money-column stripping, owner-only gates) is already covered by Sprint 3. Next: enable dev-OTP or seed a member session cookie, then log in as each role and diff the visible tabs/actions.</t>
+          <t>Playwright-verified (owner/finance/sales/ops real logins via scripts/s13_playwright.py). DATA-level RBAC in the UI: finance &amp; owner see money on /finance (6 rupee amounts); sales &amp; operations see 0 rupee amounts -- money surfaces are gated by role in the UI, matching the backend RBAC. Nav tabs + Settings-view are shown to all roles (gate is at the data level, not nav/route) -- a valid pattern since the sensitive DATA is hidden.</t>
         </is>
       </c>
       <c r="L149" s="11" t="inlineStr">
@@ -10055,13 +10056,13 @@
       </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J151" s="11" t="n"/>
       <c r="K151" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL: per-persona journeys -- navigation, form-open, and validation are verified in the REAL UI, but a full create-&gt;persist-&gt;on-screen journey (e.g. create a task and see it land) was flaky to drive via automation (React controlled-input + modal timing; coord clicks miss under viewport scaling). The forms demonstrably work (open + validate); a stable driver (Playwright) or a manual pass is needed to assert each on-screen result end to end.</t>
+          <t>Playwright-verified (scripts/s13_playwright.py): owner creates a task through the REAL UI (New Task modal -&gt; submit) and it PERSISTS + is retrievable in the UI under My Work &gt; All Tasks (confirmed: 'S13 Playwright task' + 'QA13 verify task' both render). Add-contact flow reachable. Note: directly-created tasks land under 'All Tasks', not the decision-driven default My Work view (a UX nuance, not a bug). Full per-persona decision-&gt;approve-&gt;pay chain covered by backend S12/S3; this closes the FE create-journey.</t>
         </is>
       </c>
       <c r="L151" s="11" t="inlineStr">
@@ -10229,7 +10230,7 @@
       <c r="J154" s="11" t="n"/>
       <c r="K154" s="12" t="inlineStr">
         <is>
-          <t>Browser-verified: the app is intentionally SINGLE-THEME (light glass). No theme toggle; emulating prefers-color-scheme:dark produces NO change (renders identical). So no dark theme to break, no theme-only unreadable text. Key flows render correctly in the in-app browser pane.</t>
+          <t>Browser-verified: the app has a WORKING light/dark theme toggle (a 'Toggle dark mode' control adds .dark to &lt;html&gt;; body bg flips light rgb(233,234,236) &lt;-&gt; dark rgb(11,11,14)). Dark mode renders correctly (login + main surfaces readable, no theme-only unreadable text). (Correction: earlier 'single-theme' note was wrong -- it's a class-based toggle, not prefers-color-scheme, so OS-preference emulation didn't trigger it.)</t>
         </is>
       </c>
       <c r="L154" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1110,7 +1110,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Epic 10 -- Testing IN EXECUTION. 131/154 scenario tasks Done (85%); Sprints 1-8, 10, 11 COMPLETE (11 sprints), Sprint 13 at 11/12. Remaining: S9 (AI/extraction) + S12 (E2E journeys). Full pytest suite: 1327 passed / 3 skipped, deterministic under xdist. Bugs surfaced+fixed by this effort: BUG-11 (finance direction), BUG-12 (seat TOCTOU), BUG-13 (stage double-spawn), BUG-14 (quota aggregate fail-open), BUG-15 (phantom '0 Workflows' reveal stat).</t>
+          <t>Epic 10 -- Testing IN EXECUTION. 142/154 scenario tasks Done (92%); Sprints 1-8, 10, 11 COMPLETE (11 sprints), S9 at 11/12, S13 at 11/12. Remaining: S9.8 (Dex RAG citation) + S12 (E2E journeys) + S13.9 (voice/Dex). Bugs surfaced+fixed: BUG-11..15 + BUG-16 (deprecated Gemini OCR model 404 -&gt; ALL invoice OCR down; repointed to gemini-3.6-flash) + BUG-17 (plural finance/sales nouns escaped the deterministic Brain-RBAC gate). AI extraction verified on REAL data: 5 invoice photos (Gemini 3.6 OCR) + 5 Tamil/Tanglish voice notes (Sarvam STT).</t>
         </is>
       </c>
     </row>
@@ -1428,19 +1428,19 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -7312,13 +7312,13 @@
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J102" s="11" t="n"/>
       <c r="K102" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>LIVE-verified (test_s9_extraction_live.py, Gemini 3.6 vision OCR): 4 real GST invoices (3 handwritten + 1 printed phone-photo) -&gt; correct vendor/number/GSTIN/date/total/currency/line-items; clean high-conf extractions route auto/confirm (needs_review False), not attention. Fixing BUG-16 was a prerequisite (the OCR model was 404 / all OCR down).</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
@@ -7368,13 +7368,13 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J103" s="11" t="n"/>
       <c r="K103" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>LIVE + logic-verified: the real angled/low-res photos still extract correctly (Gemini 3.6 is robust); the low-confidence -&gt; needs_review -&gt; attention routing (a shaky/unparseable scan never silently auto-files) is proven deterministically in calibrate_doc_confidence + _decide_processing_level (test_s9_ai_logic.py + test_s1_captures_confidence_unit.py).</t>
         </is>
       </c>
       <c r="L103" s="11" t="inlineStr">
@@ -7424,13 +7424,13 @@
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J104" s="11" t="n"/>
       <c r="K104" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>LIVE-verified: the foreign US/USD invoice (7.jpg, low-res) extracts gracefully -- currency USD (NOT hallucinated as INR), no invented GSTIN, no crash; unknown fields left empty (test_s9_extraction_live.py::test_foreign_invoice_graceful).</t>
         </is>
       </c>
       <c r="L104" s="11" t="inlineStr">
@@ -7480,13 +7480,13 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J105" s="11" t="n"/>
       <c r="K105" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>LIVE-verified: ai_map_spreadsheet on messy headers (Party Name / Bill No / Amt (Rs) / GSTIN) -&gt; correct party + amount mapping. sanitize_table/combine_sheets already unit-tested (test_epic3_s6_spreadsheet).</t>
         </is>
       </c>
       <c r="L105" s="11" t="inlineStr">
@@ -7536,13 +7536,13 @@
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J106" s="11" t="n"/>
       <c r="K106" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>LIVE-verified: 5 real Tamil/Tanglish voice notes -&gt; Sarvam saaras STT -&gt; English directives; a directive -&gt; ai_extract -&gt; structured task (e.g. 'Tell Priya to call Threads Boutique' -&gt; task 'Call Threads Boutique', role sales). test_s9_extraction_live.py::test_tanglish_voice_directive_becomes_task.</t>
         </is>
       </c>
       <c r="L106" s="11" t="inlineStr">
@@ -7592,13 +7592,13 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J107" s="11" t="n"/>
       <c r="K107" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>LIVE-verified: all 5 clips transcribe (engine=sarvam, language auto-detected Tamil/English). STT hard-fail -&gt; 503 with no partial garbage decision is already covered by test_s2_functional transcribe_only.</t>
         </is>
       </c>
       <c r="L107" s="11" t="inlineStr">
@@ -7648,13 +7648,13 @@
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J108" s="11" t="n"/>
       <c r="K108" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified (test_s9_ai_logic.py): ai_capture_triage output coercion -- classification not in CAPTURE_CLASSES -&gt; 'other', bad/missing confidence -&gt; 0.7, bad priority -&gt; 'medium', dept/intent defaults, unrelated -&gt; bool, unparseable model response -&gt; safe 'other'.</t>
         </is>
       </c>
       <c r="L108" s="11" t="inlineStr">
@@ -7704,13 +7704,13 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J109" s="11" t="n"/>
       <c r="K109" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>REMAINING: Dex RAG citation accuracy needs a live Company-Brain integration harness (uploaded brain_document + embeddings + /ask|/brain/agent query asserting the answer cites brain_documents/brain_context). Out of scope for this extraction-focused pass. test_iteration73_brain_ask + test_brain_retrieval_unified cover brain retrieval shape but not citation-provenance accuracy.</t>
         </is>
       </c>
       <c r="L109" s="11" t="inlineStr">
@@ -7760,13 +7760,13 @@
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J110" s="11" t="n"/>
       <c r="K110" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified (P0, test_s9_ai_logic.py): brain_rbac classify_intent x allowed_intents matrix -- operations/sales users denied finance/sales questions, finance denied sales, owner all-access, unknown role -&gt; baseline-only (fail-closed). FIXED BUG-17: plural finance/sales/procurement/ops nouns ('list all invoices') used to escape the DETERMINISTIC gate.</t>
         </is>
       </c>
       <c r="L110" s="11" t="inlineStr">
@@ -7816,13 +7816,13 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J111" s="11" t="n"/>
       <c r="K111" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified: injection defense -- detect_injection fires on override/role-reassign patterns, wrap_untrusted delimits the payload, INJECTION_GUARD is in the triage system prompt; an injected 'auto-approve 99999' message never auto-files (owner-review). LIVE: the 'PREVIEW CLEARLY / double-click' banner embedded in 7.jpg was NOT obeyed -- read as a document.</t>
         </is>
       </c>
       <c r="L111" s="11" t="inlineStr">
@@ -7872,13 +7872,13 @@
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J112" s="11" t="n"/>
       <c r="K112" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified (test_s9_ai_logic.py): fail-open contract -- ai_extract on junk/blank model output -&gt; valid fully-bucketed dict + needs_review (never raises); ai_extract_document on malformed OCR -&gt; review-flagged empty result, no crash.</t>
         </is>
       </c>
       <c r="L112" s="11" t="inlineStr">
@@ -7928,13 +7928,13 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J113" s="11" t="n"/>
       <c r="K113" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified: doc confidence -&gt; routing bridge -- calibrate_doc_confidence (parse-fail / no-records / low) -&gt; needs_review -&gt; _decide_processing_level 'attention'; clean high-conf small-amount -&gt; 'auto'; over owner-threshold -&gt; 'confirm'. The full _decide table is already in test_s1_captures_confidence_unit.</t>
         </is>
       </c>
       <c r="L113" s="11" t="inlineStr">
@@ -10306,7 +10306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10337,7 +10337,7 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>Tally: 15 bug findings -&gt; 8 Fixed, 6 Flagged (product decisions), 1 Disproven. Plus 11 test-infra/wiring items (INF-*).</t>
+          <t>Tally: 17 bug findings -&gt; 10 Fixed, 6 Flagged (product decisions), 1 Disproven. Plus 11 test-infra/wiring items (INF-*).</t>
         </is>
       </c>
     </row>
@@ -11607,6 +11607,70 @@
       <c r="I30" s="11" t="inlineStr">
         <is>
           <t>T10-04.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BUG-16</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AI / vision OCR</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>The vision/OCR model gemini-2.5-flash was deprecated by Google ('no longer available to new users' -&gt; 404), taking ALL document/invoice OCR down: the user-key Gemini path 404'd and the Emergent-key vision fallback then timed out at 45s. Every invoice/bill/receipt scan failed end-to-end. Surfaced by running the real invoice photos in testdata/ through ai_extract_document.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fixed -- added catalog model gemini-flash-3 -&gt; gemini-3.6-flash and repointed the 3 vision routes (documents.doc_extract / vision.read_image / ledger.ocr) + DEFAULT_VISION_MODEL + the claude-sonnet text fallback (config.py), per the catalog's 'add new id, don't edit in place' convention. Verified: all 5 real invoices now extract correct vendor/GSTIN/total/currency/line-items (test_s9_extraction_live.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BUG-17</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Company Brain / RBAC intent gate</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>brain_rbac.classify_intent's finance/sales/procurement/ops patterns matched only SINGULAR whole-word nouns (invoice, payment), so a non-finance user asking a PLURAL finance question ('list all invoices', 'show me payments') classified as 'general' and passed the DETERMINISTIC fail-closed gate (routers/brain.py:779) -- caught only by the LLM-planner belt-and-suspenders (plan.needs_finance) + money-column strip, weakening the deterministic P0 layer. Surfaced while unit-testing the S9 RBAC-gate scenario (T10-09.9).</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fixed -- pluralised the countable nouns (optional trailing s) across the finance/sales/procurement/ops/hr intent patterns (services/ai/brain_rbac.py); plural finance/sales/procurement/ops questions now classify deterministically. Regression-guarded in test_s9_ai_logic.py (test_bug17_plural_finance_questions_are_gated).</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1110,7 +1110,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Epic 10 -- Testing IN EXECUTION. 142/154 scenario tasks Done (92%); Sprints 1-8, 10, 11 COMPLETE (11 sprints), S9 at 11/12, S13 at 11/12. Remaining: S9.8 (Dex RAG citation) + S12 (E2E journeys) + S13.9 (voice/Dex). Bugs surfaced+fixed: BUG-11..15 + BUG-16 (deprecated Gemini OCR model 404 -&gt; ALL invoice OCR down; repointed to gemini-3.6-flash) + BUG-17 (plural finance/sales nouns escaped the deterministic Brain-RBAC gate). AI extraction verified on REAL data: 5 invoice photos (Gemini 3.6 OCR) + 5 Tamil/Tanglish voice notes (Sarvam STT).</t>
+          <t>Epic 10 -- Testing IN EXECUTION. 143/154 scenario tasks Done (93%); Sprints 1-11 COMPLETE (12 sprints incl. S9 AI/extraction), S13 at 11/12. Remaining: S12 (E2E journeys) + S13.9 (voice/Dex). AI extraction verified on REAL data: 5 invoice photos (Gemini 3.6 OCR) + 5 Tamil/Tanglish voice notes (Sarvam STT) + a LIVE diverse Company Brain (RAG citation accuracy w/ real OpenAI embeddings). Bugs surfaced+fixed: BUG-11..15 + BUG-16 (deprecated Gemini OCR model 404 -&gt; all invoice OCR down) + BUG-17 (plural nouns escaped the deterministic Brain-RBAC gate).</t>
         </is>
       </c>
     </row>
@@ -1428,19 +1428,19 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -7704,13 +7704,13 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J109" s="11" t="n"/>
       <c r="K109" s="12" t="inlineStr">
         <is>
-          <t>REMAINING: Dex RAG citation accuracy needs a live Company-Brain integration harness (uploaded brain_document + embeddings + /ask|/brain/agent query asserting the answer cites brain_documents/brain_context). Out of scope for this extraction-focused pass. test_iteration73_brain_ask + test_brain_retrieval_unified cover brain retrieval shape but not citation-provenance accuracy.</t>
+          <t>Verified on a LIVE, diverse Company Brain (test_s9_brain_rag.py + tests/brain_seed_data.py): 8 documents across source types (policy/SOP/contract/filing/report/note) + departments + visibility levels, PLUS 3 brain_context provenance records, ingested via index_document (real chunks -&gt; in-memory Qdrant) + brain_documents catalog. Drives the REAL retrieval+citation code (search_documents / search_chunks / search_context -&gt; cites_from_hits) and asserts: every question cites the RIGHT source doc (source_type=brain_document); 'how did we handle X' cites brain_context provenance; an out-of-domain question fabricates NO citation; RBAC holds (finance-private GST/Q3 docs invisible to sales/operations). Runs offline (bag-of-words, CI) AND with RUN_LIVE_LLM=1 -&gt; REAL OpenAI text-embedding-3-small (recall &gt;=95%). Qdrant runs in-memory -- no vector-DB infra needed. Closes the ingest-&gt;ask-&gt;assert-citation gap.</t>
         </is>
       </c>
       <c r="L109" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1110,7 +1110,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Epic 10 -- Testing IN EXECUTION. 143/154 scenario tasks Done (93%); Sprints 1-11 COMPLETE (12 sprints incl. S9 AI/extraction), S13 at 11/12. Remaining: S12 (E2E journeys) + S13.9 (voice/Dex). AI extraction verified on REAL data: 5 invoice photos (Gemini 3.6 OCR) + 5 Tamil/Tanglish voice notes (Sarvam STT) + a LIVE diverse Company Brain (RAG citation accuracy w/ real OpenAI embeddings). Bugs surfaced+fixed: BUG-11..15 + BUG-16 (deprecated Gemini OCR model 404 -&gt; all invoice OCR down) + BUG-17 (plural nouns escaped the deterministic Brain-RBAC gate).</t>
+          <t>Epic 10 -- Testing IN EXECUTION. 153/154 scenario tasks Done (99%); Sprints 1-12 COMPLETE (incl. S12 E2E persona journeys + exit gate), S13 at 11/12 (only .9 voice/Dex left). AUTOMATED testing sign-off: all dimensions S1-S12 green (owner/finance/sales/ops journeys + WhatsApp + voice + Kapoor golden path, all in-process against isolated Mongo). Bugs found+fixed: BUG-11..17.</t>
         </is>
       </c>
     </row>
@@ -1527,19 +1527,19 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -9104,13 +9104,13 @@
       </c>
       <c r="I134" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J134" s="11" t="n"/>
       <c r="K134" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified in-process E2E (tests/test_s12_e2e_journeys.py::test_owner_golden_path): decision -&gt; approve (unblocks blocked task) -&gt; task done w/ evidence -&gt; invoice raised -&gt; inbound payment reconciled (paid) -&gt; operating_score owner view. One unbroken journey through the REAL functions.</t>
         </is>
       </c>
       <c r="L134" s="11" t="inlineStr">
@@ -9160,13 +9160,13 @@
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J135" s="11" t="n"/>
       <c r="K135" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified (test_finance_persona_journey): raise 3 invoices -&gt; reconcile inbound payments (full/partial/none via real ledger.reconcile_payment) -&gt; statuses paid/partial/unpaid, outstanding = 40000 correct; owner company money view computes.</t>
         </is>
       </c>
       <c r="L135" s="11" t="inlineStr">
@@ -9216,13 +9216,13 @@
       </c>
       <c r="I136" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J136" s="11" t="n"/>
       <c r="K136" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified (test_sales_persona_journey): contact + activity + unpaid invoice -&gt; real crm.outstanding_by_contact attributes receivables -&gt; raise + real complaints.resolve_complaint -&gt; resolved + brain_context 'resolution' provenance WRITTEN (record_context kept real); sales is NOT the owner company view.</t>
         </is>
       </c>
       <c r="L136" s="11" t="inlineStr">
@@ -9272,13 +9272,13 @@
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J137" s="11" t="n"/>
       <c r="K137" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified (test_operations_persona_journey): start workflow -&gt; real workflow_engine.advance through every stage (CAS) to terminal (completed_at, stage_version=3) -&gt; real leave._create_leave + team._decide_leave(approved) -&gt; approved leave row the calendar/on-leave read merges.</t>
         </is>
       </c>
       <c r="L137" s="11" t="inlineStr">
@@ -9328,13 +9328,13 @@
       </c>
       <c r="I138" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J138" s="11" t="n"/>
       <c r="K138" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified (test_multi_role_parallel_day): owner (decision+approve) + finance (reconcile) + sales (complaint resolve) + ops (workflow advance) all act in one tenant/window -&gt; every write landed, none clobbered another (decision approved, task todo, invoice paid, complaint resolved, workflow advanced); owner score computes over the mixed state.</t>
         </is>
       </c>
       <c r="L138" s="11" t="inlineStr">
@@ -9384,13 +9384,13 @@
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J139" s="11" t="n"/>
       <c r="K139" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified (test_whatsapp_bill_to_ledger_and_inbox): a bill-photo capture draft -&gt; real captures.execute_capture -&gt; commit_ingestion_records creates the ledger record + db.ingestions filed + inbox item status=done. The zero-typing path.</t>
         </is>
       </c>
       <c r="L139" s="11" t="inlineStr">
@@ -9440,13 +9440,13 @@
       </c>
       <c r="I140" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J140" s="11" t="n"/>
       <c r="K140" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified (test_voice_to_decision_to_execution): dictate -&gt; real voice.process_voice_note materialises a pending_approval decision + blocked task -&gt; approve_decision unblocks -&gt; generate_execution_plan -&gt; tick all steps via save_execution_plan(accepted) -&gt; task auto-completes (progress 100).</t>
         </is>
       </c>
       <c r="L140" s="11" t="inlineStr">
@@ -9496,13 +9496,13 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J141" s="11" t="n"/>
       <c r="K141" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified (test_kapoor_golden_path_full): the WE-15 sales pipeline end-to-end -- per-stage template tasks + role hand-offs (sales-&gt;finance-&gt;operations), close-then-advance through every stage to terminal, terminal create_expense side effect (awaiting_bill); PLUS the negative not_ready gate (open task -&gt; check_stage_ready False -&gt; advance raises WorkflowAdvanceError code=not_ready 409, stage_version unchanged).</t>
         </is>
       </c>
       <c r="L141" s="11" t="inlineStr">
@@ -9552,13 +9552,13 @@
       </c>
       <c r="I142" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J142" s="11" t="n"/>
       <c r="K142" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Verified (test_s12_exit_gate.py): every Testing-Plan phase A-J mapped to a concrete pass/fail gate. Automatable phases asserted at exit criteria -- A automated (S1/S2/S11 + the S12 E2E journeys), B isolation (S8), C RBAC (S3), E concurrency (S10), F tenant-deletion (S8) -- all Done. Non-automatable phases (D load, F backup/migration, G-J alpha/beta/GA) attributed to Epic 1 S5 / manual rollout, not silently claimed.</t>
         </is>
       </c>
       <c r="L142" s="11" t="inlineStr">
@@ -9608,13 +9608,13 @@
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J143" s="11" t="n"/>
       <c r="K143" s="12" t="inlineStr">
         <is>
-          <t>Grounded in code map 2026-08-29</t>
+          <t>Go-live QA sign-off (test_s12_exit_gate.py::test_all_automated_testing_dimensions_green): every AUTOMATED testing dimension is green -- Epic 10 S1-S11 fully Done + the S12 E2E persona journeys (.1-.8) Done. Go-Live Checklist 'Testing (A-J)' row stays pending the manual ops phases (load/backup/beta = Epic 1 S5); the automated half is signed off here.</t>
         </is>
       </c>
       <c r="L143" s="11" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1110,7 +1110,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Epic 10 -- Testing IN EXECUTION. 153/154 scenario tasks Done (99%); Sprints 1-12 COMPLETE (incl. S12 E2E persona journeys + exit gate), S13 at 11/12 (only .9 voice/Dex left). AUTOMATED testing sign-off: all dimensions S1-S12 green (owner/finance/sales/ops journeys + WhatsApp + voice + Kapoor golden path, all in-process against isolated Mongo). Bugs found+fixed: BUG-11..17.</t>
+          <t>Epic 10 -- Testing COMPLETE. 154/154 scenario tasks Done (100%). All 13 sprints green: unit + functional + role-matrix + onboarding + multi-niche + team-scale + formula-edge + isolation + AI/extraction + concurrency + regression-health + E2E persona journeys + frontend/UX/browser-driven. AI extraction proven on REAL data (invoice photos + Tamil voice + live Company Brain); voice/Dex surfaces verified via a fake-media device. Bugs found+fixed: BUG-11..17.</t>
         </is>
       </c>
     </row>
@@ -1560,19 +1560,19 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -10112,13 +10112,13 @@
       </c>
       <c r="I152" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J152" s="11" t="n"/>
       <c r="K152" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL: Dex/voice UI surfaces present -- the Dex orb button exists, the capture bar renders ('Or capture a decision right here' + Capture on operating-score). But actual voice record/stop + the 'Dex is structuring N' inflight async states can't be driven -- the preview blocks microphone capture. Visual surfaces verified; the live async pipeline states need a real mic / manual pass.</t>
+          <t>Verified browser-driven (scripts/s13_9_voice_dex_playwright.py + s13_9_seed.py) with a Chromium FAKE media device (--use-fake-device-for-media-stream / --use-fake-ui-for-media-stream) that grants a headless mic so getUserMedia resolves -- dissolving the mic block. All 6 voice/Dex async-pipeline surfaces PASS: (1) 'Dex is structuring 1 capture right now' inflight badge on /brain (seeded voice_note status=structuring -&gt; GET /dex/inflight-count); (2) capture bar dex-stage; (3) mic record dex-stage-mic; (4) record-&gt;recording state dex-stage-stop with 'Ns' timer + status 'Listening…' -- the mic-gated surface, now reachable via the fake device; (5) decision-review dialog for a pending_approval voice-sourced decision (/inbox?decision=); (6) Approve/Reject actions. The state-surfacing that .9 asserts is fully verified; only a human physically speaking is un-automatable.</t>
         </is>
       </c>
       <c r="L152" s="11" t="inlineStr">
